--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4431025114) وتاريخ 1/1/1445هـ الصادر عن الدائرة الأولى بالمحكمة التجارية بجدة في الدعوى المقيدة برقم (42824717) وتاريخ 25/12/1442هـ ـ 1/1/1445هـ</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,16 +589,36 @@
           <t>حكم / صك</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4431025114</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1007056847؛ 1008017301؛ 1017092733؛ 144442؛ 2824717؛ 42824717؛ 4431025114</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -763,7 +783,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4630548401) وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، والقاضي بعدم قبول الالتماس المقدم بالطلب رقم (4611037394) وتاريخ 02/06/1446ه</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -771,18 +791,50 @@
           <t>حكم / صك</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4630548401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1007056847؛ 1008017301؛ 1017092733؛ 42824717؛ 4611037394؛ 4630548401</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -881,12 +933,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>إقرار من السيدة/ عاتقة محمد يحي حرازي مؤرخ في 04/03/1445هـ، ممهور ببصمتها، بأنها أوكلت المحامِ (محمد فواز الثعلي) وكيلًا عنها، وعدم صحة الادعاء بحجزها ـ 04/03/1445هـ</t>
+          <t>اقرار من الوالدة عاتقة توكيل الثعلي في الدعوى 42824717 ضد اسامة زيني ـ 04-03-1445.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>وكالة</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -985,24 +1037,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>آلية تنفيذ بتاريخ 09/02/1434هـ الموافق 22/12/2012م لدى فضيلة القاضي/ علي القريقري، قاضي التنفيذ بالمحكمة العامة بجدة [وذلك فيما يتعلق بنقل كل من طرفي النزاع الشركات التي اختص بها ك</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3004840892019؛ 3308000358؛ 8160648</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>36.8160648.91؛ 17.698.860.51؛ 3004840892019</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -1185,7 +1257,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى ا</t>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى المقيدة برقم (42824717) وقضية أرض التنس.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1943,26 +2015,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>مسودة التماس إعادة النظر المقدم على صك الاستئناف الصادر في الدعوى رقم (42824717) وتاريخ 25/12/1442هـ. ـ 25/12/1442هـ</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>4530828230؛ 4630548401</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>42824717؛ 4530828230؛ 4571443116؛ 4630371972؛ 4630548401؛ 4731461703؛ 4771864931</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>24/04/1446</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>16؛ 17؛ 18؛ 76؛ 86؛ 89؛ 94؛ 95؛ 200</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -2015,7 +2123,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4,690,483؛ 2,463,761</t>
+          <t>2,463,761؛ 4,690,483</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2073,7 +2181,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1,400,000.00؛ 250,000,000؛ 172,613,467؛ 217,250,000؛ 39,495,773؛ 11,679,151؛ 21,659,786؛ 1,073,0000؛ 33,573,786؛ 17,635,241؛ 28,977,000؛ 172,613466؛ 2,500,000؛ 1,000,000؛ 1,943,903؛ 5,850,000؛ 1,900,000؛ 1,974,805؛ 100000000؛ 1,170,000؛ 1,527,778؛ 20000000؛ 2,900,00؛ 466,000؛ 300.000</t>
+          <t>1,400,000.00؛ 217,250,000؛ 172,613,467؛ 250,000,000؛ 11,679,151؛ 33,573,786؛ 1,073,0000؛ 172,613466؛ 21,659,786؛ 28,977,000؛ 17,635,241؛ 39,495,773؛ 2,500,000؛ 1,000,000؛ 5,850,000؛ 1,527,778؛ 1,900,000؛ 100000000؛ 1,943,903؛ 1,170,000؛ 1,974,805؛ 20000000؛ 2,900,00؛ 590,000؛ 300.000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2123,7 +2231,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1,037259,019؛ 172,613,467؛ 11,679,151؛ 14,282,008؛ 1,943,903؛ 3,062,129؛ 856,255؛ 737,500؛ 390,000</t>
+          <t>1,037259,019؛ 172,613,467؛ 14,282,008؛ 11,679,151؛ 1,943,903؛ 3,062,129؛ 737,500؛ 390,000؛ 856,255</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2255,7 +2363,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى المقيدة برقم (199058) وتاريخ 18/06/1445هـ لدى المجلس الأعلى للقضاء ـ 18/06/1445هـ</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2263,18 +2371,50 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>199058؛ 42824717؛ 4530241622</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1445/06/18؛ 1445/11/13</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -2327,7 +2467,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>500.000؛ 500,000؛ 450000؛ 1000</t>
+          <t>500,000؛ 500.000؛ 450000؛ 1000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2385,15 +2525,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>تقرير العيوطي — وُجد بتاريخ 11/06/2026م ضمن مجلد مرفقات مذكرة الالتماس بين المورث وعبد الله آبار، وتقترح الدراسة نقض تقرير أبو غزالة به ـ —</t>
+          <t>تقييم العيوطي للشركات.pdf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -2449,7 +2593,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17,698,860,51؛ 36,816,648,91؛ 18,408,324,46؛ 15,242,446,10؛ 30484,89219؛ 8,849430,25؛ 500,000,1؛ 18,08346؛ 100,000</t>
+          <t>36,816,648,91؛ 15,242,446,10؛ 18,408,324,46؛ 17,698,860,51؛ 8,849430,25؛ 30484,89219؛ 500,000,1؛ 18,08346؛ 100,000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2593,7 +2737,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار المطالبة المالية بمبلغ 96,779,270</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2601,15 +2745,39 @@
           <t>إخطار مطالبة</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1008017301؛ 1017092733؛ 1098908278؛ 27651219؛ 440300010192؛ 4530241622؛ 556355663؛ 96779270</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>27651219؛ 96779270</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -2801,7 +2969,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>120,000,000؛ 368,000,000؛ 450,000</t>
+          <t>368,000,000؛ 120,000,000؛ 450,000</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3105,7 +3273,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>368,757,931؛ 79,924,901؛ 137631,929؛ 331882.138؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 450؛ 120</t>
+          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3137,7 +3305,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3145,16 +3313,36 @@
           <t>مذكرة قضائية</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>310041499400003؛ 42824717؛ 4714487917؛ 6550303؛ 6550707؛ 6554777</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1447/09/02</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
@@ -3209,7 +3397,7 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>120,000,000؛ 368,000,000؛ 450,000</t>
+          <t>368,000,000؛ 120,000,000؛ 450,000</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3299,7 +3487,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم إبراء الذمة ـ 22-07-1447</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3307,16 +3495,32 @@
           <t>حكم / صك</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1007056847؛ 1008017301؛ 1017092733؛ 144447؛ 401024501240718؛ 4630371972؛ 4713404041؛ 4713765960؛ 4731639254؛ 4731814153؛ 77186464931</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1447/07/22</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
@@ -3663,7 +3867,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>طلب النقض الأخير ـ 07-10-1447</t>
+          <t>طلب النقض الاحير المقدم في 07-10-1447 ـ القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3797,7 +4001,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا ـ 25-02-1445</t>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3805,18 +4009,38 @@
           <t>حكم / صك</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1008017301؛ 1064274077؛ 451560570</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف / دائرة الاستئناف؛ ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -3941,26 +4165,54 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>مذكرة التماس إلحاقية ـ 08-08-1445</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>42824717؛ 4530241622</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>79,924,901</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>47؛ 69؛ 78؛ 185</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -3975,7 +4227,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>مذكرة التماس الشهري 13-07-1445 ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3983,18 +4235,46 @@
           <t>مذكرة قضائية</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1008017301؛ 1064274077؛ 42824717؛ 451560570</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف / دائرة الاستئناف؛ ديوان المظالم؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4009,7 +4289,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامة</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4017,18 +4297,58 @@
           <t>مذكرة قضائية</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3218883؛ 33286392؛ 3855849؛ 4030196102؛ 42824717؛ 4530241622</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>120,000,000</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>26؛ 78</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4175,26 +4495,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 10-04-1445 ـ مرفق عقود التخارج</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1008017301؛ 1064274077؛ 42824717؛ 451560570</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف / دائرة الاستئناف؛ ديوان المظالم؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4391,24 +4735,48 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>مذكرة جوابية ـ 16-08-1445</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>42824717؛ 4530241622</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>20,043,862</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
@@ -4483,7 +4851,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم (عدنان وعاتقة)</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4491,16 +4859,40 @@
           <t>مذكرة قضائية</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1007056847؛ 1008017301؛ 1017092733؛ 42824717؛ 447042453؛ 45700530093</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
@@ -4617,7 +5009,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>100000000؛ 500,000؛ 500.000؛ 450,000؛ 5000000؛ 92,000؛ 46,000؛ 1000؛ 120؛ 500؛ 450؛ 000؛ 310</t>
+          <t>100000000؛ 450,000؛ 500,000؛ 500.000؛ 5000000؛ 46,000؛ 92,000؛ 1000؛ 120؛ 500؛ 310؛ 450؛ 000</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -4821,7 +5213,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>500.000؛ 500,000؛ 1000</t>
+          <t>500,000؛ 500.000؛ 1000</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -4949,7 +5341,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>500,000؛ 500.000؛ 450,000؛ 1000</t>
+          <t>500.000؛ 450,000؛ 500,000؛ 1000</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5197,7 +5589,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>مرفق 8 ـ مذكرة أبو راشد ـ 25-04-1443</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5205,16 +5597,32 @@
           <t>مذكرة قضائية</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>16554777؛ 310041499400003؛ 42824717؛ 6550303؛ 6550707؛ 6554777</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
@@ -5979,7 +6387,7 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>372.426.828؛ 368.757.931؛ 335,184,145؛ 27,932,012؛ 97,762,042؛ 450.000</t>
+          <t>335,184,145؛ 368.757.931؛ 372.426.828؛ 27,932,012؛ 97,762,042؛ 450.000</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6255,7 +6663,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>التماس في الدعوى ـ نسخة ثانية</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6263,18 +6671,50 @@
           <t>مذكرة قضائية</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1007056847؛ 1008017301؛ 1017092733؛ 42824717</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>27/06/2011</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>200؛ 201</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -6327,7 +6767,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>4,690,483؛ 2,463,761</t>
+          <t>2,463,761؛ 4,690,483</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6347,7 +6787,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>جزء من مسحوبات مصروفات الشيخ أحمد</t>
+          <t>جزء من مسحوبات مصروفات الشيخ احمد زيني رحمه الله.pdf</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6355,7 +6795,11 @@
           <t>مستند مالي</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
@@ -6419,7 +6863,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>جزء من مصروفات فيلا الوادي</t>
+          <t>جزء من مصروفات فيلا الوادي.pdf</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6427,7 +6871,11 @@
           <t>مستند مالي</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
@@ -7083,22 +7531,34 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>مصاريف المزرعة (Excel)</t>
+          <t>مصاريف مزرعة الشيخ أحمد زيني بالوادي (1).xlsx</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>01/11/1432؛ 04/03/1434؛ 05/11/1431؛ 06/08/1433؛ 07/02/1433؛ 07/03/1433؛ 07/07/1433؛ 07/09/1433؛ 10/06/1434؛ 11/02/1431؛ 12/05/1434؛ 12/10/1434؛ 13/01/1431؛ 13/03/1432؛ 13/08/1431؛ 14/10/1432؛ 15/04/1432؛ 15/04/1434؛ 15/08/1434؛ 16/11/1431؛ 17/07/1431؛ 18/04/1431؛ 19/03/1432؛ 19/05/1433؛ 19/06/1432</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>10/12/2012؛ 10/2/2014؛ 10/3/2011؛ 10/3/2013؛ 10/4/2013؛ 10/5/2011؛ 11/3/2015؛ 11/4/2011؛ 11/6/2011؛ 11/7/2012؛ 11/8/2012؛ 11/9/2012؛ 12/1/2014؛ 12/10/2011؛ 12/2/2011؛ 12/2/2013؛ 12/3/2014؛ 12/7/2011؛ 12/9/2011؛ 13/02/2010؛ 13/02/2012؛ 13/03/2012؛ 13/4/2014؛ 13/4/2015؛ 13/5/2010</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
@@ -7253,22 +7713,34 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>مصاريف فيلا الوادي (Excel)</t>
+          <t>excelمصاريف فيلا الشيخ أحمد زيني بالوادي.xlsx</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>01-11-1432؛ 05-11-1431؛ 06-08-1433؛ 07-02-1433؛ 07-03-1433؛ 07-07-1433؛ 07-09-1433؛ 13-03-1432؛ 14-10-1432؛ 15-04-1432؛ 16-11-1431؛ 19-03-1432؛ 19-05-1433؛ 19-06-1432؛ 19-10-1433؛ 20-01-1432؛ 20-05-1432؛ 20-07-1432؛ 21-12-1433؛ 22-08-1432؛ 22-11-1432؛ 27-04-1433؛ 27-12-1432؛ 28-03-1433؛ 29-11-1433</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>02/12/2011؛ 03/10/2011؛ 04/07/2012؛ 04/11/2011؛ 05/08/2012؛ 05/10/2011؛ 06/09/2012؛ 06/11/2011؛ 07/11/2012؛ 07/12/2011؛ 08/11/2012؛ 09/11/2012؛ 09/12/2011؛ 10/09/2012؛ 10/12/2011؛ 12/01/2015؛ 13/02/2012؛ 13/03/2012؛ 14/01/2012؛ 14/10/2010؛ 14/12/2011؛ 15/08/2011؛ 15/09/2010؛ 16/01/2011؛ 16/11/2011</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
@@ -7429,7 +7901,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>100000000؛ 500.000؛ 450,000؛ 46,000؛ 50000؛ 1000؛ 500؛ 000؛ 310؛ 120</t>
+          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 120؛ 500؛ 310؛ 000</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -7461,7 +7933,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>موجز الشكوى للمجلس الأعلى</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7469,16 +7941,36 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0556355663؛ 1008017301؛ 183821؛ 199058؛ 230747621؛ 401024200266155؛ 42824717</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1445/01/05؛ 1445/04/30؛ 1445/06/18</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
@@ -7533,7 +8025,7 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -7607,7 +8099,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 450؛ 120</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -7685,7 +8177,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>368,757,931؛ 79,924,901؛ 137631,929؛ 331882.138؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 450؛ 120</t>
+          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -7941,7 +8433,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>100000000؛ 500,000؛ 500.000؛ 450,000؛ 46,000؛ 1000؛ 500؛ 310؛ 120</t>
+          <t>100000000؛ 500,000؛ 450,000؛ 500.000؛ 46,000؛ 1000؛ 120؛ 500؛ 310</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8023,7 +8515,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>100000000؛ 500.000؛ 450,000؛ 46,000؛ 50000؛ 1000؛ 500؛ 000؛ 310؛ 120</t>
+          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 120؛ 500؛ 310؛ 000</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8055,7 +8547,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8063,18 +8555,54 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>000844؛ 1008017301؛ 401024501215577؛ 401024501240718؛ 421170332؛ 42824717؛ 4530241622</t>
+        </is>
+      </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>04/10/2010</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>450,000؛ 120</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام القضاء</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>3؛ 21؛ 80؛ 85؛ 141</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8089,7 +8617,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ 13-11-1445</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8097,18 +8625,66 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>محمد الثعلي (وكيل)؛ القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8447,7 +9023,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>500,000؛ 500.000؛ 1000</t>
+          <t>500.000؛ 500,000؛ 1000</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -8521,7 +9097,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 450؛ 120</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -8757,7 +9333,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8765,18 +9341,66 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>محمد الثعلي (وكيل)؛ القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8841,7 +9465,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 450؛ 120</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -8939,7 +9563,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى (صورة)</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8947,18 +9571,50 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>199058؛ 42824717؛ 4530241622</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1445/06/18؛ 1445/11/13</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9077,7 +9733,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9085,18 +9741,66 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>محمد الثعلي (وكيل)؛ القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 13 - 11 - 1445؛ 13 / 03 / 1445؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9149,7 +9853,7 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -9481,7 +10185,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -9559,7 +10263,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 450؛ 120</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -9703,24 +10407,44 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل ـ 19-06-1445</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>230747621؛ 42824717</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1445/06/19</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
@@ -9787,7 +10511,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>36877936؛ 79929906؛ 150,000؛ 17,000؛ 120؛ 450؛ 268؛ 200؛ 138</t>
+          <t>79929906؛ 36877936؛ 150,000؛ 17,000؛ 268؛ 120؛ 200؛ 450؛ 138</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10039,7 +10763,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 450؛ 120</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -10071,7 +10795,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد (وورد)</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10079,17 +10803,41 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>42824717؛ 4530241622</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
@@ -10105,7 +10853,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>مذكرة الالتماس ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10113,13 +10861,25 @@
           <t>مذكرة قضائية</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>1008017301؛ 1064274077؛ 451560570</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1445/03/20؛ 1446/03/20</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -1005,7 +1005,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>331,882,138؛ 368,757,931؛ 450,000؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 450,000؛ 120</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3700,000,000؛ 120,000,000؛ 370,000,000؛ 450,000؛ 5000000؛ 1000</t>
+          <t>3700,000,000؛ 370,000,000؛ 120,000,000؛ 450,000؛ 5000000؛ 1000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2,463,761؛ 4,690,483</t>
+          <t>4,690,483؛ 2,463,761</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1,400,000.00؛ 217,250,000؛ 172,613,467؛ 250,000,000؛ 11,679,151؛ 33,573,786؛ 1,073,0000؛ 172,613466؛ 21,659,786؛ 28,977,000؛ 17,635,241؛ 39,495,773؛ 2,500,000؛ 1,000,000؛ 5,850,000؛ 1,527,778؛ 1,900,000؛ 100000000؛ 1,943,903؛ 1,170,000؛ 1,974,805؛ 20000000؛ 2,900,00؛ 590,000؛ 300.000</t>
+          <t>1,400,000.00؛ 250,000,000؛ 172,613,467؛ 217,250,000؛ 39,495,773؛ 21,659,786؛ 33,573,786؛ 17,635,241؛ 1,073,0000؛ 11,679,151؛ 172,613466؛ 28,977,000؛ 1,527,778؛ 1,974,805؛ 5,850,000؛ 2,500,000؛ 1,900,000؛ 100000000؛ 1,000,000؛ 1,943,903؛ 1,170,000؛ 2,900,00؛ 20000000؛ 590,000؛ 147,500</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1,037259,019؛ 172,613,467؛ 14,282,008؛ 11,679,151؛ 1,943,903؛ 3,062,129؛ 737,500؛ 390,000؛ 856,255</t>
+          <t>1,037259,019؛ 172,613,467؛ 11,679,151؛ 14,282,008؛ 1,943,903؛ 3,062,129؛ 390,000؛ 856,255؛ 737,500</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>500,000؛ 500.000؛ 450000؛ 1000</t>
+          <t>500.000؛ 500,000؛ 450000؛ 1000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>36,816,648,91؛ 15,242,446,10؛ 18,408,324,46؛ 17,698,860,51؛ 8,849430,25؛ 30484,89219؛ 500,000,1؛ 18,08346؛ 100,000</t>
+          <t>18,408,324,46؛ 17,698,860,51؛ 15,242,446,10؛ 36,816,648,91؛ 30484,89219؛ 8,849430,25؛ 500,000,1؛ 18,08346؛ 100,000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>100000000؛ 450,000؛ 500,000؛ 500.000؛ 5000000؛ 46,000؛ 92,000؛ 1000؛ 120؛ 500؛ 310؛ 450؛ 000</t>
+          <t>100000000؛ 500,000؛ 500.000؛ 5000000؛ 450,000؛ 46,000؛ 92,000؛ 1000؛ 450؛ 120؛ 000؛ 310؛ 500</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>500,000؛ 500.000؛ 1000</t>
+          <t>500.000؛ 500,000؛ 1000</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>500.000؛ 450,000؛ 500,000؛ 1000</t>
+          <t>500.000؛ 500,000؛ 450,000؛ 1000</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6387,7 +6387,7 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>335,184,145؛ 368.757.931؛ 372.426.828؛ 27,932,012؛ 97,762,042؛ 450.000</t>
+          <t>368.757.931؛ 372.426.828؛ 335,184,145؛ 97,762,042؛ 27,932,012؛ 450.000</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6453,7 +6453,7 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>368.757.931؛ 27,932,012؛ 97,762,042؛ 450.000</t>
+          <t>368.757.931؛ 97,762,042؛ 27,932,012؛ 450.000</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2,463,761؛ 4,690,483</t>
+          <t>4,690,483؛ 2,463,761</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -7138,18 +7138,42 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>000539؛ 000545؛ 0010001؛ 00437103؛ 010111011101111؛ 010178814؛ 0146108؛ 018018؛ 030587؛ 0397042؛ 04001395؛ 0445198؛ 047514111؛ 0509420128؛ 0557567836؛ 0558851484؛ 090010111؛ 1010035319؛ 10548056؛ 1070001411؛ 10815800؛ 110815800؛ 110954877؛ 1110111؛ 11200111</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1434/06/30؛ 1434/11/24؛ 1454/05/9</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>01/07/2013؛ 01/08/2013؛ 01/09/2013؛ 01/10/2013؛ 01/11/2013؛ 01/12/2013؛ 03-06-2013؛ 1-1-2013؛ 2013/09/30؛ 26-8-2013؛ 26/06/2013؛ 26/08/2013؛ 27-5-2013؛ 28/06/2013؛ 29-05-2013؛ 30/06/2014؛ 30/08/2014؛ 31-12-2013؛ 31/08/2013؛ 91/07/2013</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>17,000؛ 20,000؛ 1000؛ 250</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
@@ -7172,18 +7196,42 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>000714؛ 000880012900005؛ 00589873؛ 0062014؛ 0070000؛ 0100176819؛ 010018515؛ 011410147؛ 02072014؛ 022723؛ 046811228329؛ 1001363؛ 1010035319؛ 10815800؛ 11095405؛ 11710111؛ 12045253؛ 12139284؛ 192014؛ 20131222؛ 209912؛ 209915؛ 212224؛ 247714161507؛ 4000178881</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1435-11-02؛ 1435/02/01؛ 1435/02/07؛ 1435/06/30؛ 1435/08/11؛ 1435/12/20؛ 1435/12/21؛ 1435/12/25؛ 1435/12/27</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>01/07/2014؛ 01/08/2014؛ 01/09/2014؛ 01/10/2014؛ 01/11/2014؛ 01/12/2014؛ 02/07/2014؛ 07/10/2014؛ 08/10/2014؛ 10/15/2014؛ 15/12/2013؛ 15/9/2014؛ 17/9/2014؛ 18/10/2014؛ 20/9/2014؛ 2013/12/04؛ 2013/12/10؛ 2014/06/09؛ 21/09/2014؛ 21/9/2014؛ 22/9/2014؛ 23/09/2014؛ 23/9/2014؛ 24/09/2014؛ 24/9/2014</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>25,000؛ 30,000؛ 22,500؛ 36,171؛ 20,000؛ 2.000؛ 1.000؛ 3.325؛ 1902؛ 1013؛ 250</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
@@ -7206,18 +7254,42 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>د. محمد البنا؛ المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>000001؛ 00002298؛ 00002323؛ 00002339؛ 0110180514؛ 01116100419580؛ 01501210026؛ 0202020202022؛ 0202202000؛ 022723؛ 0235586؛ 0468112222؛ 047544؛ 0498455؛ 0564115؛ 056415؛ 05864115؛ 061009؛ 100008173؛ 100027382؛ 10011000؛ 10031100؛ 100630659؛ 100806138؛ 10095160</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>02/10/1435؛ 02/11/1435؛ 08/02/1435؛ 08/04/1434؛ 12/03/1434؛ 14/11/1433؛ 1436/02/04؛ 1436/03/13؛ 1436/04/20؛ 1436/06/05؛ 1436/06/13؛ 1436/06/20؛ 1436/06/26؛ 1436/08/28؛ 20/03/1435؛ 23/06/1435؛ 25/12/1434</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>01/10/2014؛ 06/11/2014؛ 07/10/2014؛ 08/10/2014؛ 09/02/2015؛ 09/04/2015؛ 1/7/2015؛ 10/12/2014؛ 14/06/2015؛ 15/04/2015؛ 15/12/2014؛ 18/10/2014؛ 2014/11/26؛ 2015-01-07؛ 2015/02/09؛ 2015/04/02؛ 2015/1/29؛ 2015/1/7؛ 2015/2/1؛ 2015/2/10؛ 2015/2/25؛ 2015/3/15؛ 2015/3/18؛ 2015/3/25؛ 2015/3/26</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>60,000؛ 26,100؛ 30,000؛ 60,900؛ 25,096؛ 20,000</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
@@ -7240,18 +7312,42 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>000001؛ 000016؛ 00002368؛ 00002374؛ 00002405؛ 00002430؛ 00002436؛ 00002476؛ 0003000000000030000؛ 0006001؛ 000880012900005؛ 00501716؛ 0057356952297500081؛ 010010000؛ 0100176714؛ 020338؛ 020500118598؛ 022723؛ 0468112222؛ 0468112226؛ 046811286996؛ 052000؛ 05864115؛ 10011000؛ 10031100</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>02/10/1435؛ 02/11/1435؛ 06/01/1437؛ 08/02/1435؛ 13/02/1435؛ 1436/08/11؛ 1436/10/17؛ 1436/10/19؛ 1436/11/10؛ 1437-01-02؛ 1437/01/01؛ 1437/01/29؛ 1437/03/19؛ 1437/03/20؛ 16/03/1436؛ 18/05/1433؛ 19/09/1436؛ 20/03/1435؛ 21/03/1437؛ 21/07/1436؛ 23/06/1435؛ 25/12/1434؛ 29/03/1436؛ 29/11/1436</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>01/10/2014؛ 03/09/2015؛ 06-07-2015؛ 06/11/2014؛ 07/10/2014؛ 08/10/2014؛ 09/02/2015؛ 09/04/2015؛ 10-11-2015؛ 10/12/2014؛ 10/5/2015؛ 15/04/2015؛ 18/10/2014؛ 19/08/2015؛ 2015/07/29؛ 2015/10/19؛ 2015/10/8؛ 2015/11/12؛ 2015/12/10؛ 2015/12/29؛ 2015/12/31؛ 2015/14/17؛ 2015/4/29؛ 2015/7/29؛ 2015/8/10</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>13,908.10؛ 16,623.26؛ 40901050؛ 60,000؛ 10,000؛ 57,120؛ 31,000</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
@@ -7307,7 +7403,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>685؛ 198</t>
+          <t>198؛ 685</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7400,18 +7496,42 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0000000؛ 0000277؛ 000028؛ 077782؛ 095535؛ 107812؛ 109355؛ 110003317؛ 110035317؛ 11112200110187463؛ 111432؛ 113257؛ 115777؛ 15050197؛ 17095141916؛ 17554195؛ 17594197؛ 4030092091؛ 5100007102؛ 519175؛ 539553؛ 552588؛ 555115؛ 5597115؛ 5801715</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>03/05/1433؛ 1/2/1433؛ 1/3/1433؛ 1433/02/20؛ 1433/03/21؛ 1433/04/20؛ 1433/05/15؛ 1433/06/17؛ 1433/07/19؛ 1433/08/21؛ 1433/09/23؛ 1433/10/24؛ 1433/11/23؛ 25/2/1412؛ 3/1/1433</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2011/12/14؛ 2012/01/14؛ 2012/02/13؛ 2012/03/13؛ 2012/04/07؛ 2012/05/08؛ 2012/06/09؛ 2012/07/11؛ 2012/08/11؛ 2012/09/11؛ 2012/10/09</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>10851</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
@@ -7434,17 +7554,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>006582؛ 008929؛ 019519؛ 059551916؛ 095160؛ 11100321؛ 1451241؛ 172602031؛ 20000000؛ 2001200؛ 2002006؛ 200266؛ 206950؛ 210090؛ 210200؛ 210250؛ 250115؛ 4030092091؛ 420821915251؛ 5059115؛ 519175؛ 54419118؛ 5451911؛ 5495191؛ 552081</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>14/03/1434؛ 1434/02/26؛ 1434/04/02؛ 1434/04/28؛ 1434/05/29؛ 1434/07/27؛ 1434/10/08</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2012/12/10؛ 2013/01/08؛ 2013/02/12؛ 2013/03/10؛ 2013/04/10؛ 2013/06/06؛ 2013/08/15</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
@@ -7468,18 +7608,42 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>000259517؛ 002622؛ 010955؛ 012000؛ 022291؛ 023641؛ 023698؛ 023700؛ 050955؛ 093535؛ 100251؛ 100253؛ 10052261؛ 1100551؛ 12106500؛ 130295؛ 155560؛ 1955601؛ 202000؛ 2022161؛ 2062015؛ 206210؛ 210220؛ 21022001؛ 210250</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1435/01/06؛ 1435/03/11؛ 1435/04/10؛ 1435/05/11؛ 1435/06/13؛ 22/02/1435</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2/16/2014؛ 2013/11/09؛ 2014/01/12؛ 2014/02/10؛ 2014/03/12؛ 2014/04/13</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>9290؛ 9240</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
@@ -7502,17 +7666,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>000000011؛ 000061؛ 043305؛ 044191؛ 0911516؛ 100115751؛ 1002179؛ 100222؛ 1005517؛ 10095195؛ 10095198؛ 110202219؛ 111005519؛ 119810؛ 120035519؛ 12320234؛ 191850؛ 202210؛ 2022162؛ 206620؛ 2100600؛ 2102216؛ 2106215؛ 2106216؛ 2209972600</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1436/03/23؛ 1436/6/24؛ 1436/8/21؛ 1436/9/27</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2015/01/14؛ 2015/06/09؛ 2015/07/14؛ 2015/3/11؛ 2015/4/13؛ 2015/6/3؛ 2015/7/27؛ 2015/7/29</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
@@ -7650,18 +7834,42 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>المحامي الشهري</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0000230؛ 000024؛ 000025؛ 000028؛ 009535؛ 009555؛ 010955؛ 012000؛ 050533؛ 077729797901؛ 100002219؛ 107022؛ 11003317؛ 119171؛ 1371151941؛ 1555519116؛ 18300564؛ 1980111؛ 200002؛ 200006؛ 20006000؛ 20026200؛ 200600؛ 2006000؛ 20060000</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>03/05/1433؛ 1/2/1433؛ 1433/02/20؛ 1433/03/21؛ 1433/04/20؛ 1433/05/15؛ 1433/06/17؛ 1433/07/19؛ 1433/08/21؛ 1433/09/23؛ 1433/10/24؛ 1433/11/23؛ 15/05/1433؛ 15/1/1433؛ 26/11/1432؛ 3/1/1433؛ 3/6/1433؛ 4/4/1433</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2011/12/14؛ 2012/01/14؛ 2012/02/13؛ 2012/03/13؛ 2012/04/07؛ 2012/05/08؛ 2012/06/09؛ 2012/07/11؛ 2012/08/11؛ 2012/09/11؛ 2012/10/09</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>19,000,500؛ 350.00؛ 01318</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
@@ -7687,15 +7895,31 @@
           <t>غير مصنف</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>000000؛ 10011000؛ 10095160؛ 10095720؛ 10095722؛ 10095725؛ 10095727؛ 10095742؛ 10095749؛ 111614؛ 4801009؛ 500112؛ 50561715؛ 5056415؛ 5056515؛ 50582715؛ 514595؛ 514745؛ 514945؛ 51569511؛ 55017115؛ 554115؛ 55617915؛ 6065216</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2015/12/1؛ 2015/7/29؛ 2015/8/30؛ 2015/9/20</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>5.56415</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
@@ -7825,13 +8049,29 @@
           <t>شكوى</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>230747621؛ 42824717</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1445/04/30</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
@@ -7901,7 +8141,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 120؛ 500؛ 310؛ 000</t>
+          <t>100000000؛ 500.000؛ 450,000؛ 46,000؛ 50000؛ 1000؛ 120؛ 000؛ 310؛ 500</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8025,7 +8265,7 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>450؛ 120</t>
+          <t>120؛ 450</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -8099,7 +8339,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8177,7 +8417,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8433,7 +8673,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>100000000؛ 500,000؛ 450,000؛ 500.000؛ 46,000؛ 1000؛ 120؛ 500؛ 310</t>
+          <t>100000000؛ 500,000؛ 500.000؛ 450,000؛ 46,000؛ 1000؛ 120؛ 310؛ 500</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8515,7 +8755,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 120؛ 500؛ 310؛ 000</t>
+          <t>100000000؛ 500.000؛ 450,000؛ 46,000؛ 50000؛ 1000؛ 120؛ 000؛ 310؛ 500</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8667,7 +8907,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9097,7 +9337,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9250,7 +9490,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>غير مصنف</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -9258,8 +9498,16 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>199058</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1445/06/18</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
@@ -9383,7 +9631,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9465,7 +9713,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9783,7 +10031,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -9853,7 +10101,7 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>450؛ 120</t>
+          <t>120؛ 450</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10185,7 +10433,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>450؛ 120</t>
+          <t>120؛ 450</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -10263,7 +10511,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10511,7 +10759,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>79929906؛ 36877936؛ 150,000؛ 17,000؛ 268؛ 120؛ 200؛ 450؛ 138</t>
+          <t>79929906؛ 36877936؛ 150,000؛ 17,000؛ 200؛ 450؛ 120؛ 138؛ 268</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10763,7 +11011,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -1067,7 +1067,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>36.8160648.91؛ 17.698.860.51؛ 3004840892019</t>
+          <t>3004840892019؛ 36.8160648.91؛ 17.698.860.51</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3700,000,000؛ 370,000,000؛ 120,000,000؛ 450,000؛ 5000000؛ 1000</t>
+          <t>3700,000,000؛ 120,000,000؛ 370,000,000؛ 5000000؛ 450,000؛ 1000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4,690,483؛ 2,463,761</t>
+          <t>2,463,761؛ 4,690,483</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1,400,000.00؛ 250,000,000؛ 172,613,467؛ 217,250,000؛ 39,495,773؛ 21,659,786؛ 33,573,786؛ 17,635,241؛ 1,073,0000؛ 11,679,151؛ 172,613466؛ 28,977,000؛ 1,527,778؛ 1,974,805؛ 5,850,000؛ 2,500,000؛ 1,900,000؛ 100000000؛ 1,000,000؛ 1,943,903؛ 1,170,000؛ 2,900,00؛ 20000000؛ 590,000؛ 147,500</t>
+          <t>1,400,000.00؛ 172,613,467؛ 250,000,000؛ 217,250,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 172,613466؛ 11,679,151؛ 1,073,0000؛ 17,635,241؛ 1,974,805؛ 1,170,000؛ 5,850,000؛ 1,527,778؛ 2,500,000؛ 100000000؛ 1,900,000؛ 1,943,903؛ 1,000,000؛ 2,900,00؛ 20000000؛ 350,000؛ 650,000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1,037259,019؛ 172,613,467؛ 11,679,151؛ 14,282,008؛ 1,943,903؛ 3,062,129؛ 390,000؛ 856,255؛ 737,500</t>
+          <t>1,037259,019؛ 172,613,467؛ 11,679,151؛ 14,282,008؛ 3,062,129؛ 1,943,903؛ 856,255؛ 737,500؛ 390,000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18,408,324,46؛ 17,698,860,51؛ 15,242,446,10؛ 36,816,648,91؛ 30484,89219؛ 8,849430,25؛ 500,000,1؛ 18,08346؛ 100,000</t>
+          <t>36,816,648,91؛ 18,408,324,46؛ 15,242,446,10؛ 17,698,860,51؛ 30484,89219؛ 8,849430,25؛ 500,000,1؛ 18,08346؛ 100,000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>27651219؛ 96779270</t>
+          <t>96779270؛ 27651219</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>368,000,000؛ 120,000,000؛ 450,000</t>
+          <t>120,000,000؛ 368,000,000؛ 450,000</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>368,757,931؛ 79,924,901؛ 331882.138؛ 137631,929؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3397,7 +3397,7 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>368,000,000؛ 120,000,000؛ 450,000</t>
+          <t>120,000,000؛ 368,000,000؛ 450,000</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3880,11 +3880,19 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>4714689866</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العليا</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
@@ -5009,7 +5017,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>100000000؛ 500,000؛ 500.000؛ 5000000؛ 450,000؛ 46,000؛ 92,000؛ 1000؛ 450؛ 120؛ 000؛ 310؛ 500</t>
+          <t>100000000؛ 5000000؛ 450,000؛ 500.000؛ 500,000؛ 46,000؛ 92,000؛ 1000؛ 500؛ 120؛ 000؛ 450؛ 310</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5341,7 +5349,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>500.000؛ 500,000؛ 450,000؛ 1000</t>
+          <t>500.000؛ 450,000؛ 500,000؛ 1000</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6387,7 +6395,7 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>368.757.931؛ 372.426.828؛ 335,184,145؛ 97,762,042؛ 27,932,012؛ 450.000</t>
+          <t>368.757.931؛ 335,184,145؛ 372.426.828؛ 27,932,012؛ 97,762,042؛ 450.000</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6453,7 +6461,7 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>368.757.931؛ 97,762,042؛ 27,932,012؛ 450.000</t>
+          <t>368.757.931؛ 27,932,012؛ 97,762,042؛ 450.000</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6767,7 +6775,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>4,690,483؛ 2,463,761</t>
+          <t>2,463,761؛ 4,690,483</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -7229,7 +7237,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>25,000؛ 30,000؛ 22,500؛ 36,171؛ 20,000؛ 2.000؛ 1.000؛ 3.325؛ 1902؛ 1013؛ 250</t>
+          <t>22,500؛ 25,000؛ 30,000؛ 36,171؛ 20,000؛ 1.000؛ 2.000؛ 3.325؛ 1902؛ 1013؛ 250</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7287,7 +7295,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>60,000؛ 26,100؛ 30,000؛ 60,900؛ 25,096؛ 20,000</t>
+          <t>60,900؛ 26,100؛ 60,000؛ 25,096؛ 30,000؛ 20,000</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7345,7 +7353,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>13,908.10؛ 16,623.26؛ 40901050؛ 60,000؛ 10,000؛ 57,120؛ 31,000</t>
+          <t>16,623.26؛ 13,908.10؛ 40901050؛ 57,120؛ 60,000؛ 10,000؛ 31,000</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7641,7 +7649,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>9290؛ 9240</t>
+          <t>9240؛ 9290</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8141,7 +8149,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>100000000؛ 500.000؛ 450,000؛ 46,000؛ 50000؛ 1000؛ 120؛ 000؛ 310؛ 500</t>
+          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 500؛ 120؛ 000؛ 310</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8265,7 +8273,7 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -8339,7 +8347,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8417,7 +8425,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331882.138؛ 137631,929؛ 79,924,901؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>368,757,931؛ 79,924,901؛ 331882.138؛ 137631,929؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8673,7 +8681,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>100000000؛ 500,000؛ 500.000؛ 450,000؛ 46,000؛ 1000؛ 120؛ 310؛ 500</t>
+          <t>100000000؛ 450,000؛ 500.000؛ 500,000؛ 46,000؛ 1000؛ 500؛ 120؛ 310</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8755,7 +8763,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>100000000؛ 500.000؛ 450,000؛ 46,000؛ 50000؛ 1000؛ 120؛ 000؛ 310؛ 500</t>
+          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 500؛ 120؛ 000؛ 310</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8907,7 +8915,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9337,7 +9345,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9631,7 +9639,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9713,7 +9721,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9783,7 +9791,7 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10031,7 +10039,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10101,7 +10109,7 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10433,7 +10441,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -10511,7 +10519,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10759,7 +10767,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>79929906؛ 36877936؛ 150,000؛ 17,000؛ 200؛ 450؛ 120؛ 138؛ 268</t>
+          <t>36877936؛ 79929906؛ 150,000؛ 17,000؛ 120؛ 200؛ 450؛ 138؛ 268</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10829,7 +10837,7 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>120؛ 450</t>
+          <t>450؛ 120</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11011,7 +11019,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 450؛ 120؛ 368</t>
+          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -1067,7 +1067,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3004840892019؛ 36.8160648.91؛ 17.698.860.51</t>
+          <t>3,004,840,892,019؛ 36,816,064,891؛ 1,769,886,051</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3700,000,000؛ 120,000,000؛ 370,000,000؛ 5000000؛ 450,000؛ 1000</t>
+          <t>3,700,000,000؛ 370,000,000؛ 120,000,000؛ 5,000,000؛ 450,000؛ 1,000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2,463,761؛ 4,690,483</t>
+          <t>4,690,483؛ 2,463,761</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1,400,000.00؛ 172,613,467؛ 250,000,000؛ 217,250,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 172,613466؛ 11,679,151؛ 1,073,0000؛ 17,635,241؛ 1,974,805؛ 1,170,000؛ 5,850,000؛ 1,527,778؛ 2,500,000؛ 100000000؛ 1,900,000؛ 1,943,903؛ 1,000,000؛ 2,900,00؛ 20000000؛ 350,000؛ 650,000</t>
+          <t>250,000,000؛ 217,250,000؛ 172,613,467؛ 172,613,466؛ 140,000,000؛ 100,000,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 20,000,000؛ 17,635,241؛ 11,679,151؛ 10,730,000؛ 5,850,000؛ 2,500,000؛ 1,974,805؛ 1,943,903؛ 1,900,000؛ 1,527,778؛ 1,170,000؛ 1,000,000؛ 900,000؛ 856,255؛ 833,333</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1,037259,019؛ 172,613,467؛ 11,679,151؛ 14,282,008؛ 3,062,129؛ 1,943,903؛ 856,255؛ 737,500؛ 390,000</t>
+          <t>1,037,259,019؛ 172,613,467؛ 14,282,008؛ 11,679,151؛ 3,062,129؛ 1,943,903؛ 856,255؛ 737,500؛ 390,000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>500.000؛ 500,000؛ 450000؛ 1000</t>
+          <t>500,000؛ 450,000؛ 1,000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>36,816,648,91؛ 18,408,324,46؛ 15,242,446,10؛ 17,698,860,51؛ 30484,89219؛ 8,849430,25؛ 500,000,1؛ 18,08346؛ 100,000</t>
+          <t>3,681,664,891؛ 3,048,489,219؛ 1,840,832,446؛ 1,769,886,051؛ 1,524,244,610؛ 884,943,025؛ 5,000,001؛ 1,808,346؛ 100,000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>96779270؛ 27651219</t>
+          <t>96,779,270؛ 27,651,219</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>120,000,000؛ 368,000,000؛ 450,000</t>
+          <t>368,000,000؛ 120,000,000؛ 450,000</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>368,757,931؛ 79,924,901؛ 331882.138؛ 137631,929؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3397,7 +3397,7 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>120,000,000؛ 368,000,000؛ 450,000</t>
+          <t>368,000,000؛ 120,000,000؛ 450,000</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3463,7 +3463,7 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1,445</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>100000000؛ 5000000؛ 450,000؛ 500.000؛ 500,000؛ 46,000؛ 92,000؛ 1000؛ 500؛ 120؛ 000؛ 450؛ 310</t>
+          <t>100,000,000؛ 5,000,000؛ 500,000؛ 450,000؛ 92,000؛ 46,000؛ 1,000؛ 120</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>500.000؛ 500,000؛ 1000</t>
+          <t>500,000؛ 1,000</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>500.000؛ 450,000؛ 500,000؛ 1000</t>
+          <t>500,000؛ 450,000؛ 1,000</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6395,7 +6395,7 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>368.757.931؛ 335,184,145؛ 372.426.828؛ 27,932,012؛ 97,762,042؛ 450.000</t>
+          <t>372,426,828؛ 368,757,931؛ 335,184,145؛ 97,762,042؛ 27,932,012؛ 450,000</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6461,7 +6461,7 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>368.757.931؛ 27,932,012؛ 97,762,042؛ 450.000</t>
+          <t>368,757,931؛ 97,762,042؛ 27,932,012؛ 450,000</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2,463,761؛ 4,690,483</t>
+          <t>4,690,483؛ 2,463,761</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>17,000؛ 20,000؛ 1000؛ 250</t>
+          <t>20,000؛ 17,000؛ 1,000</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>22,500؛ 25,000؛ 30,000؛ 36,171؛ 20,000؛ 1.000؛ 2.000؛ 3.325؛ 1902؛ 1013؛ 250</t>
+          <t>36,171؛ 30,000؛ 25,000؛ 22,500؛ 20,000؛ 3,325؛ 2,000؛ 1,902؛ 1,013؛ 1,000</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>60,900؛ 26,100؛ 60,000؛ 25,096؛ 30,000؛ 20,000</t>
+          <t>60,900؛ 60,000؛ 30,000؛ 26,100؛ 25,096؛ 20,000</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>16,623.26؛ 13,908.10؛ 40901050؛ 57,120؛ 60,000؛ 10,000؛ 31,000</t>
+          <t>40,901,050؛ 1,662,326؛ 1,390,810؛ 60,000؛ 57,120؛ 31,000؛ 10,000</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7409,11 +7409,7 @@
           <t>01/07/2014؛ 01/07/2015؛ 02/10/2015؛ 03/01/2015؛ 03/03/2013؛ 03/03/2015؛ 03/09/2015؛ 04/05/2010؛ 05/04/2015؛ 05/08/2015؛ 06/05/2013؛ 06/09/2014؛ 07/01/2015؛ 08/06/2015؛ 08/07/2014؛ 08/07/2015؛ 08/09/2015؛ 08/10/2015؛ 09/03/2015؛ 09/06/2014؛ 09/08/2015؛ 10/01/2013؛ 10/02/2015؛ 10/03/2010؛ 10/05/2010</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>198؛ 685</t>
-        </is>
-      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
@@ -7537,7 +7533,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10,851</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7649,7 +7645,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>9240؛ 9290</t>
+          <t>9,290؛ 9,240</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -7875,7 +7871,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>19,000,500؛ 350.00؛ 01318</t>
+          <t>19,000,500؛ 35,000؛ 1,318</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -7925,7 +7921,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>5.56415</t>
+          <t>556,415</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -8149,7 +8145,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 500؛ 120؛ 000؛ 310</t>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8347,7 +8343,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8425,7 +8421,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>368,757,931؛ 79,924,901؛ 331882.138؛ 137631,929؛ 20,200,00؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8681,7 +8677,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>100000000؛ 450,000؛ 500.000؛ 500,000؛ 46,000؛ 1000؛ 500؛ 120؛ 310</t>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8763,7 +8759,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>100000000؛ 450,000؛ 500.000؛ 46,000؛ 50000؛ 1000؛ 500؛ 120؛ 000؛ 310</t>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8915,7 +8911,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9213,7 +9209,7 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>100000000؛ 46,000؛ 1000؛ 310</t>
+          <t>100,000,000؛ 46,000؛ 1,000</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -9271,7 +9267,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>500.000؛ 500,000؛ 1000</t>
+          <t>500,000؛ 1,000</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -9345,7 +9341,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9639,7 +9635,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9721,7 +9717,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10039,7 +10035,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10519,7 +10515,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10767,7 +10763,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>36877936؛ 79929906؛ 150,000؛ 17,000؛ 120؛ 200؛ 450؛ 138؛ 268</t>
+          <t>79,929,906؛ 36,877,936؛ 150,000؛ 17,000؛ 450؛ 268؛ 120</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11019,7 +11015,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>00000000000000؛ 137,631,929؛ 368,757931؛ 331882138؛ 20,200,00؛ 79924901؛ 150,000؛ 6061304؛ 17,000؛ 1000؛ 368؛ 120؛ 450</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1017092733؛ 144442؛ 2824717؛ 42824717؛ 4431025114</t>
+          <t>1037108001؛ 244441؛ 3372907101؛ 42824717؛ 4431025114؛ 7174282؛ 7486507001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -659,19 +659,15 @@
           <t>42824717</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 144442؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102؛ 4030196102؛ 421254094</t>
+          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 3372907101؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 09/11/1443؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1385 / 3 / 22؛ 14/ 10/ 1427؛ 14/ 3/ 1428؛ 1431-09-20</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25؛ 1432-11-07؛ 1432-12-02؛ 1432/12/2؛ 1433-06-08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -690,11 +686,7 @@
           <t>نظام التنفيذ</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -733,19 +725,15 @@
           <t>42824717</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 144442؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102؛ 4030196102؛ 421254094</t>
+          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 3372907101؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 09/11/1443؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1385 / 3 / 22؛ 14/ 10/ 1427؛ 14/ 3/ 1428؛ 1431-09-20</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25؛ 1432-11-07؛ 1432-12-02؛ 1432/12/2؛ 1433-06-08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -764,11 +752,7 @@
           <t>نظام التنفيذ</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -1771,7 +1755,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>02 / 12 / 1432؛ 10 / 02 / 1434؛ 16 / 10 / 1431</t>
+          <t>1431 / 10 / 16؛ 1432 / 12 / 02؛ 1434 / 02 / 10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3452,27 +3436,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1000017301؛ 1007056837؛ 1007056847؛ 1008017301؛ 1017092733؛ 144447؛ 27651219؛ 400344502394972؛ 401024501240718؛ 42824717؛ 4530241622؛ 466019273؛ 4731461703؛ 77186464931؛ 804332242؛ 804620836</t>
+          <t>1000017301؛ 1007056837؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 13964648177؛ 2261420354؛ 27651219؛ 3071461374؛ 400344502394972؛ 401024501240718؛ 42824717؛ 4530241622؛ 466019273؛ 744441؛ 7486507001؛ 804332242؛ 804620836</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1441 / 10 / 05؛ 1445 / 04 / 08؛ 1445 / 08 / 25؛ 1445-01-01؛ 1445/03/13؛ 1445/04/7؛ 1445/04/8؛ 1445/08/25؛ 1447 / 01 / 08؛ 1447 / 04 / 13؛ 1447/04/13</t>
+          <t>05 / 10 / 1441؛ 08 / 01 / 1447؛ 08 / 04 / 1445؛ 13 / 04 / 1447؛ 1445-01-01؛ 1445/03/13؛ 1445/04/7؛ 1445/04/8؛ 1445/08/25؛ 25 / 08 / 1445</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>1,445</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -3506,14 +3482,10 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1017092733؛ 144447؛ 401024501240718؛ 4630371972؛ 4713404041؛ 4713765960؛ 4731639254؛ 4731814153؛ 77186464931</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1447/07/22</t>
-        </is>
-      </c>
+          <t>1017092733؛ 1037108001؛ 13964648177؛ 3514181374؛ 401024501240718؛ 4630371972؛ 4713404041؛ 4713765960؛ 4731639254؛ 4731814153؛ 744441؛ 7486507001</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
@@ -3941,7 +3913,11 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>450,000</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -3952,7 +3928,11 @@
           <t>نظام المحاكم التجارية</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>3؛ 16؛ 21؛ 85</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4477,7 +4457,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>01 / 01 / 1445؛ 13 / 03 / 1445؛ 13 /3/ 1445؛ 18 /2/ 1442؛ 2/ 12 / 1431؛ 2/ 12 / 1432؛ 20 / 09 / 1431؛ 25 / 10 / 1438؛ 25 / 12 / 1442؛ 4/3/ 1432؛ 8/6/ 1432؛ 8/6/ 1433</t>
+          <t>1431 / 09 / 20؛ 1438 / 10 / 25؛ 1442 / 12 / 25؛ 1442 /2/ 18؛ 1445 / 01 / 01؛ 1445 / 03 / 13؛ 1445 /3/ 13</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -4488,7 +4468,11 @@
           <t>نظام المرافعات</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4651,12 +4635,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>04 / 03 / 1445؛ 06 / 03 / 1445</t>
+          <t>1445 / 03 / 04؛ 1445 / 03 / 06</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>21 / 09 / 2023</t>
+          <t>2023 / 09 / 21</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -4833,12 +4817,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>02 / 06 / 1446؛ 13 / 03 / 1445؛ 18 / 06 / 1446؛ 28 / 04 / 1447؛ 28 / 08 / 1447</t>
+          <t>1445 / 03 / 13؛ 1446 / 06 / 02؛ 1446 / 06 / 18؛ 1447 / 04 / 28؛ 1447 / 08 / 28</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>16 / 02 / 2026</t>
+          <t>2026 / 02 / 16</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -4945,7 +4929,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1432 - 11 - 07</t>
+          <t>07 - 11 - 1432</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
@@ -5662,22 +5646,14 @@
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
@@ -5716,22 +5692,14 @@
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011194196؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
@@ -5770,22 +5738,14 @@
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
@@ -5824,22 +5784,14 @@
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
@@ -5878,22 +5830,14 @@
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
@@ -5932,22 +5876,14 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1080215005؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 5005120801؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
@@ -5986,22 +5922,14 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
@@ -6040,22 +5968,14 @@
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12</t>
-        </is>
-      </c>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
@@ -6094,20 +6014,16 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011194196؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4403035471</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12؛ 22/10/1444</t>
+          <t>22/10/1444</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
@@ -6148,20 +6064,16 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4403035471</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12؛ 22/10/1444</t>
+          <t>22/10/1444</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -6202,20 +6114,16 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011194196؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1432-11-07؛ 1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12؛ 20/9/1431؛ 7/11/1432</t>
+          <t>1432-11-07؛ 20/9/1431؛ 7/11/1432</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -6256,20 +6164,16 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1432-11-07؛ 1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12؛ 20/9/1431؛ 7/11/1432</t>
+          <t>1432-11-07؛ 20/9/1431؛ 7/11/1432</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -6314,20 +6218,16 @@
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011194196؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 2824717؛ 3216104؛ 33286392؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3216104؛ 3307730011؛ 33286392؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>08/06/1433؛ 10/2/1434؛ 1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12؛ 22/02/1432</t>
+          <t>08/06/1433؛ 10/2/1434؛ 22/02/1432</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -6504,20 +6404,16 @@
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1011488846؛ 1017092733؛ 1044044806؛ 1056164054؛ 1064274077؛ 1073065250؛ 1097410581؛ 1098908278؛ 1099745901؛ 1100377033؛ 1111928071؛ 1122850538؛ 144442؛ 229014721194320022؛ 2824717؛ 3218883؛ 331882138؛ 33286392؛ 38391575؛ 3855849؛ 4030169102؛ 4030196102؛ 4228122</t>
+          <t>0525603701؛ 1007056847؛ 1017092733؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 229014721194320022؛ 244441؛ 3218883؛ 3307730011؛ 331882138؛ 33286392؛ 3372907101؛ 38391575؛ 3855849؛ 4030169102؛ 4030196102؛ 4228122؛ 43281449؛ 4403035471؛ 4470094084؛ 4470635209؛ 4470652975؛ 4470913988</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1/1/1445؛ 1/12/1442؛ 1/8/1444؛ 10/11/1444؛ 11/4/1437؛ 12/05/1438؛ 1434/ 7/ 26؛ 1438/ 2/ 10؛ 1438/ 4/ 21؛ 1438/ 5/ 12؛ 16/10/1431؛ 18/11/1393؛ 2/12/1432؛ 2/4/1444؛ 20/09/1431؛ 20/9/1431؛ 22/10/1444؛ 25/07/1432؛ 4/3/1432؛ 8/6/1433؛ 9/11/1443</t>
+          <t>1/1/1445؛ 1/12/1442؛ 1/8/1444؛ 10/11/1444؛ 11/4/1437؛ 12/05/1438؛ 16/10/1431؛ 18/11/1393؛ 2/12/1432؛ 2/4/1444؛ 20/09/1431؛ 20/9/1431؛ 22/10/1444؛ 25/07/1432؛ 4/3/1432؛ 8/6/1433؛ 9/11/1443</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -8130,24 +8026,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1065216؛ 1098908278؛ 137136؛ 144442؛ 2015216؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
+          <t>000000؛ 000000001؛ 0000001؛ 0000005؛ 000005؛ 000844؛ 0505620363؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 2019403016؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219؛ 3216104؛ 3218883؛ 33125567</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1385 / 3 / 22</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1413/10/26؛ 1430 / 4/4؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2010/10/04؛ 2012/10/07؛ 2023/09/20</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
-        </is>
-      </c>
+          <t>2010/10/04؛ 2023/09/20</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8158,11 +8050,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ؛ نظام القضاء</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141؛ 250</t>
-        </is>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8662,24 +8550,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1010216؛ 1017092733؛ 1030199102؛ 1065216؛ 1065416؛ 1098908278؛ 1216090؛ 137136؛ 144442؛ 2010316؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 27651219؛ 2824717؛ 30077461؛ 3216104</t>
+          <t>000000؛ 000000001؛ 0000001؛ 000005؛ 000844؛ 0505620363؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 1216090؛ 137136؛ 2019403016؛ 2019910301؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219؛ 30077461؛ 3216104</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1/ 12/ 1442؛ 1/ 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/3/ 1439؛ 12/5/1438؛ 1385 / 3 / 17</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1413/10/26؛ 1428/3/14؛ 1430 / 4/4؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2010/10/04؛ 2012/10/07؛ 2023/09/20</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>100,000,000؛ 500,000؛ 450,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
-        </is>
-      </c>
+          <t>2010/10/04؛ 2023/09/20</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8690,11 +8574,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ؛ نظام القضاء</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141؛ 250</t>
-        </is>
-      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8744,24 +8624,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1065216؛ 1098908278؛ 137136؛ 144442؛ 2015216؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
+          <t>000000؛ 000000001؛ 0000001؛ 0000005؛ 000005؛ 000844؛ 0505620363؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 2019403016؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219؛ 3216104؛ 3218883؛ 33125567</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1385 / 3 / 22</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1413/10/26؛ 1430 / 4/4؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2010/10/04؛ 2012/10/07؛ 2023/09/20</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
-        </is>
-      </c>
+          <t>2010/10/04؛ 2023/09/20</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8772,11 +8648,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ؛ نظام القضاء</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141؛ 250</t>
-        </is>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8896,24 +8768,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
-        </is>
-      </c>
+          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8924,11 +8792,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8967,19 +8831,15 @@
           <t>42824717</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 144442؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102؛ 4030196102؛ 421254094</t>
+          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 3372907101؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 09/11/1443؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1385 / 3 / 22؛ 14/ 10/ 1427؛ 14/ 3/ 1428؛ 1431-09-20</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25؛ 1432-11-07؛ 1432-12-02؛ 1432/12/2؛ 1433-06-08</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -8998,11 +8858,7 @@
           <t>نظام التنفيذ</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9326,24 +9182,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
-        </is>
-      </c>
+          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -9354,11 +9206,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9620,24 +9468,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
-        </is>
-      </c>
+          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -9648,11 +9492,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9702,24 +9542,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
-        </is>
-      </c>
+          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -9730,11 +9566,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -10020,24 +9852,20 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 13 - 11 - 1445؛ 13 / 03 / 1445؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431 / 09 / 20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
-        </is>
-      </c>
+          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -10048,11 +9876,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -10500,24 +10324,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09 / 06 / 1446؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 13 - 11 - 1445؛ 13 / 03 / 1445؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431 / 09 / 20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23؛ 30 - 10 - 2024</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
-        </is>
-      </c>
+          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024 - 10 - 30؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -10528,11 +10348,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -10748,24 +10564,20 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847؛ 104200040؛ 10550220؛ 1064274077؛ 1064690371؛ 1091304</t>
+          <t>000002؛ 00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 021290792؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 0992731؛ 10001111؛ 10001191؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431/4/20؛ 1434/11/24؛ 1436/09/20؛ 1436/09/25؛ 1437/09/20؛ 1445-01-01؛ 1445-02-12؛ 1445-02-20؛ 1445-3-13؛ 1445-4-7</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431/4/20؛ 1434/11/24؛ 1436/09/20؛ 1436/09/25؛ 1437/09/20؛ 1445-01-01؛ 1445-02-12؛ 1445-02-20؛ 1445-3-13؛ 1445-4-7؛ 1445/03/16</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>1932/12/06؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>79,929,906؛ 36,877,936؛ 150,000؛ 17,000؛ 450؛ 268؛ 120</t>
-        </is>
-      </c>
+          <t>1932/12/06؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -10776,11 +10588,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>1؛ 8؛ 96؛ 100؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -11000,24 +10808,20 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 14/ 10/ 1427؛ 14/ 3/ 1428؛ 1423/02/20</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
-        </is>
-      </c>
+          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -11028,11 +10832,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام التنفيذ</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
-        </is>
-      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -2313,12 +2313,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1447/02/13؛ 18 / 06 / 1445؛ 27 / 04 / 1446</t>
+          <t>1445 / 06 / 18؛ 1446 / 04 / 27؛ 1447/02/13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>07 / 08 / 2025؛ 2025/08/07</t>
+          <t>2025 / 08 / 07؛ 2025/08/07</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>07 / 10 / 1447؛ 09 / 09 / 1447؛ 13 / 04 / 1447؛ 29 / 04 / 1447</t>
+          <t>1447 / 04 / 13؛ 1447 / 04 / 29؛ 1447 / 09 / 09؛ 1447 / 10 / 07</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1445 / 03 / 04؛ 1445 / 03 / 06</t>
+          <t>04 / 03 / 1445؛ 06 / 03 / 1445</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2023 / 09 / 21</t>
+          <t>21 / 09 / 2023</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1445 / 03 / 13؛ 1446 / 06 / 02؛ 1446 / 06 / 18؛ 1447 / 04 / 28؛ 1447 / 08 / 28</t>
+          <t>1445 / 03 / 13؛ 1446 / 06 / 02؛ 1446 / 06 / 18؛ 1447 / 04 / 28؛ 28 / 08 / 1447</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026 / 02 / 16</t>
+          <t>16 / 02 / 2026</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -8026,20 +8026,24 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>000000؛ 000000001؛ 0000001؛ 0000005؛ 000005؛ 000844؛ 0505620363؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 2019403016؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219؛ 3216104؛ 3218883؛ 33125567</t>
+          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1037108001؛ 1065216؛ 1098908278؛ 137136؛ 2015216؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 267049؛ 27651219؛ 3216104؛ 3218883</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1413/10/26؛ 1430 / 4/4؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2010/10/04؛ 2023/09/20</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
+          <t>2010/10/04؛ 2012/10/07؛ 2023/09/20</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8050,7 +8054,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ؛ نظام القضاء</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8550,20 +8558,24 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>000000؛ 000000001؛ 0000001؛ 000005؛ 000844؛ 0505620363؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 1216090؛ 137136؛ 2019403016؛ 2019910301؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219؛ 30077461؛ 3216104</t>
+          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1010216؛ 1017092733؛ 1030199102؛ 1037108001؛ 1065216؛ 1065416؛ 1098908278؛ 1216090؛ 137136؛ 2010316؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1413/10/26؛ 1428/3/14؛ 1430 / 4/4؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/ 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/3/ 1439؛ 12/5/1438؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1428/3/14؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2010/10/04؛ 2023/09/20</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>2010/10/04؛ 2012/10/07؛ 2023/09/20</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8574,7 +8586,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ؛ نظام القضاء</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8624,20 +8640,24 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>000000؛ 000000001؛ 0000001؛ 0000005؛ 000005؛ 000844؛ 0505620363؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 2019403016؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219؛ 3216104؛ 3218883؛ 33125567</t>
+          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1037108001؛ 1065216؛ 1098908278؛ 137136؛ 2015216؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 267049؛ 27651219؛ 3216104؛ 3218883</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1413/10/26؛ 1430 / 4/4؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2010/10/04؛ 2023/09/20</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
+          <t>2010/10/04؛ 2012/10/07؛ 2023/09/20</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8648,7 +8668,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ؛ نظام القضاء</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8768,20 +8792,24 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -8792,7 +8820,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9182,20 +9214,24 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -9206,7 +9242,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9468,20 +9508,24 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -9492,7 +9536,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9542,20 +9590,24 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20؛ 1445-01-01</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -9566,7 +9618,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+        </is>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9852,7 +9908,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9862,10 +9918,14 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -9876,7 +9936,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -10324,7 +10388,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10334,10 +10398,14 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024 - 10 - 30؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024 - 10 - 30؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -10348,7 +10416,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -10564,7 +10636,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>000002؛ 00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 021290792؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 0992731؛ 10001111؛ 10001191؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847</t>
+          <t>00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847؛ 1037108001؛ 104200040؛ 10550220؛ 1064274077؛ 1064690371</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10574,10 +10646,14 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>1932/12/06؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
+          <t>1932/12/06؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>79,929,906؛ 36,877,936؛ 150,000؛ 17,000؛ 450؛ 268؛ 120</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ ديوان المظالم؛ المحكمة العليا</t>
@@ -10588,7 +10664,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>1؛ 8؛ 96؛ 100؛ 202</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -10808,20 +10888,24 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00000000360990؛ 0000008؛ 00004245695؛ 000059871؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131590049؛ 00242000؛ 00242000142؛ 007005؛ 01003021810؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 035847؛ 0392506؛ 0431102</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 / 3 / 20</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 06/08 - 2016؛ 2010/11/03؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -10832,7 +10916,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام التنفيذ</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+        </is>
+      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1037108001؛ 244441؛ 3372907101؛ 42824717؛ 4431025114؛ 7174282؛ 7486507001</t>
+          <t>1008017301؛ 144442؛ 2824717؛ 3372907101؛ 42824717؛ 4431025114؛ 7486507001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -659,10 +659,14 @@
           <t>42824717</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 3372907101؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849</t>
+          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -725,10 +729,14 @@
           <t>42824717</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 3372907101؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849</t>
+          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -989,7 +997,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 450,000؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 120</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1214,7 +1222,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0504302223؛ 1791717؛ 1792200؛ 1985888؛ 2821277؛ 4030169102؛ 42824717؛ 8687255؛ 8687266</t>
+          <t>0022971؛ 0504302223؛ 1985888؛ 2821277؛ 4030169102؛ 42824717؛ 7171971؛ 8687266</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1298,7 +1306,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1791717؛ 1792200؛ 198888؛ 2821277؛ 42824717؛ 8687255؛ 8687266</t>
+          <t>0022971؛ 42824717؛ 5527868؛ 7171971؛ 7721282؛ 8687266؛ 888891</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1522,7 +1530,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1002380507؛ 1008017301؛ 1032142174؛ 1048317232؛ 1048345209؛ 1051388؛ 180000؛ 212099؛ 229014721194320022؛ 312019؛ 312069؛ 312099؛ 319069؛ 3219104؛ 32328224؛ 33125567؛ 33286392؛ 387853؛ 567889</t>
+          <t>1008017301؛ 1032142174؛ 1048317232؛ 1048345209؛ 1051388؛ 180000؛ 229014721194320022؛ 312019؛ 312069؛ 319069؛ 3219104؛ 32328224؛ 33125567؛ 33286392؛ 387853؛ 567889؛ 7050832001؛ 910213؛ 990212؛ 990213</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1548,7 +1556,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1؛ 5؛ 6؛ 78؛ 79؛ 129؛ 239</t>
+          <t>1؛ 5؛ 6؛ 78؛ 79؛ 239</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1755,7 +1763,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1431 / 10 / 16؛ 1432 / 12 / 02؛ 1434 / 02 / 10</t>
+          <t>02 / 12 / 1432؛ 10 / 02 / 1434؛ 16 / 10 / 1431</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2150,22 +2158,22 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>000000؛ 00000000؛ 00000000014؛ 00000000016؛ 00000000020؛ 000038؛ 00011600013؛ 00037805750؛ 0006080231497؛ 001096؛ 01382699400؛ 0211318؛ 0380421؛ 0558833456؛ 10000000؛ 100000000؛ 100004242؛ 1013048699940؛ 1055022؛ 1080000؛ 110001079؛ 11323119؛ 11323368؛ 11324890؛ 1161000905</t>
+          <t>000000؛ 00000000؛ 00000000014؛ 00000000016؛ 00000000020؛ 000009؛ 000038؛ 00011600013؛ 0001212؛ 00037805750؛ 0006080231497؛ 001096؛ 00970212؛ 01382699400؛ 0211318؛ 0380421؛ 0558833456؛ 10000000؛ 100000000؛ 100004242؛ 1013048699940؛ 1055022؛ 1080000؛ 110001079؛ 11323119</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01-01-1430؛ 09/08/1431؛ 10/19/1431؛ 1411/8/30؛ 1413/10/26؛ 1423/12/30؛ 1424/9/6؛ 1426/07/18؛ 1430/10/1؛ 1432/06/07؛ 1432/4/10؛ 1432/4/30؛ 23/01/1432؛ 29-12-1430؛ 8/15/1431؛ 9/22/1431</t>
+          <t>01-01-1430؛ 09/08/1431؛ 10/19/1431؛ 1411/8/30؛ 1413/10/26؛ 1424/9/6؛ 1426/07/18؛ 1430/10/1؛ 1432/06/07؛ 1432/4/10؛ 1432/4/30؛ 23/01/1432؛ 29-12-1430؛ 8/15/1431؛ 9/22/1431</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>07-05-2011؛ 10/ 5 / 2017؛ 10/5/2011؛ 11-04-2010؛ 11-07-2010؛ 11/12/2010؛ 16-03-2010؛ 16-05-2010؛ 16-06-2010؛ 18-06-2011؛ 18-10-2010؛ 19-08-2010؛ 19-12-2010؛ 20/12/2010؛ 2003/11/1؛ 2009/04/01؛ 2009/12/21؛ 2009/12/22؛ 2010/5/1؛ 2011/5/1؛ 21-02-2011؛ 21-07-2010؛ 21/07/2010؛ 22-11-2010؛ 24-04-2011</t>
+          <t>07-05-2011؛ 10/5/2011؛ 11-04-2010؛ 11-07-2010؛ 11/12/2010؛ 16-03-2010؛ 16-05-2010؛ 16-06-2010؛ 18-06-2011؛ 18-10-2010؛ 19-08-2010؛ 19-12-2010؛ 20/12/2010؛ 2003/11/1؛ 2009/04/01؛ 2009/12/21؛ 2010/5/1؛ 2011/5/1؛ 21-02-2011؛ 21-07-2010؛ 21/07/2010؛ 22-11-2010؛ 24-04-2011؛ 26-06-2011؛ 26-09-2010</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>250,000,000؛ 217,250,000؛ 172,613,467؛ 172,613,466؛ 140,000,000؛ 100,000,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 20,000,000؛ 17,635,241؛ 11,679,151؛ 10,730,000؛ 5,850,000؛ 2,500,000؛ 1,974,805؛ 1,943,903؛ 1,900,000؛ 1,527,778؛ 1,170,000؛ 1,000,000؛ 900,000؛ 856,255؛ 833,333</t>
+          <t>250,000,000؛ 217,250,000؛ 172,613,467؛ 172,613,466؛ 140,000,000؛ 100,000,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 17,635,241؛ 11,679,151؛ 10,730,000؛ 5,850,000؛ 2,500,000؛ 1,974,805؛ 1,943,903؛ 1,900,000؛ 1,527,778؛ 1,170,000؛ 1,000,000؛ 856,255؛ 833,333؛ 650,000؛ 590,000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2208,14 +2216,14 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>037259؛ 09666685458؛ 96626685415</t>
+          <t>09666685458؛ 952730؛ 96626685415</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1,037,259,019؛ 172,613,467؛ 14,282,008؛ 11,679,151؛ 3,062,129؛ 1,943,903؛ 856,255؛ 737,500؛ 390,000</t>
+          <t>11,679,151؛ 737,500</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2566,7 +2574,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1008017301؛ 1017092733؛ 1055220915؛ 105522923؛ 1057980839؛ 199642؛ 4030016974؛ 4030042496؛ 4030048620؛ 4030054187؛ 4030092091؛ 4030092507؛ 4030092518؛ 4030094825؛ 4030107003؛ 4030107145؛ 403012010؛ 4030169102؛ 849430</t>
+          <t>010214030؛ 1008017301؛ 1017092733؛ 1055220915؛ 105522923؛ 1057980839؛ 1902900403؛ 199642؛ 2019403016؛ 3007014030؛ 4030016974؛ 4030042496؛ 4030048620؛ 4030094825؛ 4517014030؛ 7052403009؛ 7814030054؛ 8152940300؛ 849430</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2577,7 +2585,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3,681,664,891؛ 3,048,489,219؛ 1,840,832,446؛ 1,769,886,051؛ 1,524,244,610؛ 884,943,025؛ 5,000,001؛ 1,808,346؛ 100,000</t>
+          <t>3,681,664,891؛ 3,048,489,219؛ 1,840,832,446؛ 1,769,886,051؛ 1,524,244,610؛ 884,943,025؛ 5,000,001؛ 1,808,346</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3252,12 +3260,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2019/01/01؛ 2024-1-25؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3312,7 +3320,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>310041499400003؛ 42824717؛ 4714487917؛ 6550303؛ 6550707؛ 6554777</t>
+          <t>310041499400003؛ 42824717؛ 4714487917؛ 6550303؛ 6550707؛ 6554777؛ 7197471448</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3436,16 +3444,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1000017301؛ 1007056837؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 13964648177؛ 2261420354؛ 27651219؛ 3071461374؛ 400344502394972؛ 401024501240718؛ 42824717؛ 4530241622؛ 466019273؛ 744441؛ 7486507001؛ 804332242؛ 804620836</t>
+          <t>1000017301؛ 1007056837؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 13964648177؛ 2261420354؛ 27651219؛ 400344502394972؛ 401024501240718؛ 42824717؛ 4530241622؛ 466019273؛ 4731461703؛ 744441؛ 7486507001؛ 804332242؛ 804620836</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>05 / 10 / 1441؛ 08 / 01 / 1447؛ 08 / 04 / 1445؛ 13 / 04 / 1447؛ 1445-01-01؛ 1445/03/13؛ 1445/04/7؛ 1445/04/8؛ 1445/08/25؛ 25 / 08 / 1445</t>
+          <t>05 / 10 / 1441؛ 08 / 01 / 1447؛ 08 / 04 / 1445؛ 1445 / 04 / 08؛ 1445-01-01؛ 1445/03/13؛ 1445/04/7؛ 1445/04/8؛ 1445/08/25؛ 1447 / 04 / 13؛ 1447/04/13؛ 25 / 08 / 1445</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1,445</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -3482,7 +3494,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1017092733؛ 1037108001؛ 13964648177؛ 3514181374؛ 401024501240718؛ 4630371972؛ 4713404041؛ 4713765960؛ 4731639254؛ 4731814153؛ 744441؛ 7486507001</t>
+          <t>1017092733؛ 1037108001؛ 144447؛ 401024501240718؛ 4630371972؛ 4713404041؛ 4713765960؛ 4731639254؛ 4731814153؛ 7486507001؛ 77186464931</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3584,7 +3596,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1؛ 17؛ 25؛ 26؛ 200</t>
+          <t>17؛ 25؛ 26؛ 200</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -3679,7 +3691,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1447 / 04 / 13؛ 1447 / 04 / 29؛ 1447 / 09 / 09؛ 1447 / 10 / 07</t>
+          <t>07 / 10 / 1447؛ 1447 / 04 / 13؛ 1447 / 04 / 29؛ 1447 / 09 / 09</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -4024,11 +4036,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4258,11 +4266,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1431 / 09 / 20؛ 1438 / 10 / 25؛ 1442 / 12 / 25؛ 1442 /2/ 18؛ 1445 / 01 / 01؛ 1445 / 03 / 13؛ 1445 /3/ 13</t>
+          <t>01 / 01 / 1445؛ 13 / 03 / 1445؛ 13 /3/ 1445؛ 1438 / 10 / 25؛ 18 /2/ 1442؛ 2/ 12 / 1431؛ 2/ 12 / 1432؛ 20 / 09 / 1431؛ 25 / 12 / 1442؛ 8/6/ 1432؛ 8/6/ 1433</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -4526,11 +4530,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4588,11 +4588,7 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4817,7 +4813,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1445 / 03 / 13؛ 1446 / 06 / 02؛ 1446 / 06 / 18؛ 1447 / 04 / 28؛ 28 / 08 / 1447</t>
+          <t>02 / 06 / 1446؛ 13 / 03 / 1445؛ 18 / 06 / 1446؛ 28 / 04 / 1447؛ 28 / 08 / 1447</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4929,7 +4925,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>07 - 11 - 1432</t>
+          <t>1432 - 11 - 07</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
@@ -4986,12 +4982,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>000000؛ 000844؛ 0102012؛ 0126054571؛ 030420843؛ 030420883؛ 0536533388؛ 08017301؛ 100000000؛ 1007056839؛ 1007056847؛ 100801؛ 100801730؛ 1008017301؛ 1010119؛ 1015318؛ 1017092733؛ 1018219؛ 1030091825؛ 1030119102؛ 1030169102؛ 103816076؛ 1046990071؛ 1055220915؛ 1064274077</t>
+          <t>000000؛ 000000001؛ 0000005؛ 000844؛ 0102012؛ 0126054571؛ 030420843؛ 030420883؛ 0536533388؛ 08017301؛ 100000000؛ 1007056839؛ 1007056847؛ 100791؛ 100801؛ 100801730؛ 1008017301؛ 1015318؛ 1017092733؛ 1030091825؛ 1030119102؛ 1030169102؛ 103816076؛ 1046990071؛ 1055220915</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1/6/1442؛ 10 / 5 / 1436؛ 10/ 2 / 1434؛ 11/ 2 / 1434؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1413/9/8؛ 1428/3/14؛ 1428/4/18؛ 1429/12/3؛ 1430/4/4؛ 1432/11/21؛ 1432/2/13؛ 1432/6/26؛ 1438/07/26؛ 1438/3/14؛ 1438/4/18؛ 1439/12/3؛ 1442/06/28؛ 1442/5/9؛ 1445/03/13؛ 1445/03/20؛ 1446/03/20؛ 2/ 2 / 1434</t>
+          <t>1/6/1442؛ 10 / 5 / 1436؛ 11/ 2 / 1434؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1413/9/8؛ 1428/3/14؛ 1428/4/18؛ 1429/12/3؛ 1430/4/4؛ 1432/11/21؛ 1432/2/13؛ 1432/6/26؛ 1438/07/26؛ 1438/3/14؛ 1438/4/18؛ 1442/06/28؛ 1442/5/9؛ 1445/03/13؛ 1445/03/20؛ 1446/03/20؛ 2/ 2 / 1434؛ 2/15/ 1392؛ 8/ 2 / 1432</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5001,7 +4997,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>100,000,000؛ 5,000,000؛ 500,000؛ 450,000؛ 92,000؛ 46,000؛ 1,000؛ 120</t>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 1,000؛ 120</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5264,7 +5260,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>310041499400003؛ 33286392؛ 4030196102؛ 6550303؛ 6550707؛ 6554777</t>
+          <t>310041499400003؛ 33286392؛ 4030196102؛ 6550303؛ 6550707؛ 6554777؛ 7070655</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5318,7 +5314,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1008017301؛ 1030199102؛ 16554777؛ 310041499400003؛ 4030094825؛ 4030169102؛ 4030196102؛ 450000؛ 500000؛ 6065348؛ 6065431؛ 6550303؛ 6550707؛ 6554777</t>
+          <t>1008017301؛ 16554777؛ 2019910301؛ 310041499400003؛ 4030094825؛ 4030169102؛ 4030196102؛ 450000؛ 500000؛ 6065348؛ 6065431؛ 6550303؛ 6550707؛ 6554777</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5333,7 +5329,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>500,000؛ 450,000؛ 1,000</t>
+          <t>450,000؛ 1,000</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5434,7 +5430,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>16554777؛ 310041499400003؛ 42824717؛ 6550303؛ 6550707؛ 6554777</t>
+          <t>16554777؛ 310041499400003؛ 42824717؛ 6550303؛ 6550707؛ 6554777؛ 7070655</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5492,7 +5488,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>16554777؛ 310041499400003؛ 421109157؛ 421117251؛ 42824717؛ 6550303؛ 6550707؛ 6554777</t>
+          <t>16554777؛ 310041499400003؛ 421109157؛ 42824717؛ 6550303؛ 6550707؛ 6554777؛ 7070655؛ 725111124</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5510,7 +5506,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>16؛ 33؛ 76</t>
+          <t>33؛ 76</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -5646,11 +5642,15 @@
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5692,11 +5692,15 @@
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5738,11 +5742,15 @@
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5784,11 +5792,15 @@
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5830,11 +5842,15 @@
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5876,11 +5892,15 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 5005120801؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 5005120801؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5922,11 +5942,15 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5968,11 +5992,15 @@
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -6014,11 +6042,15 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6064,11 +6096,15 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6114,11 +6150,15 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6164,11 +6204,15 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6218,11 +6262,15 @@
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 244441؛ 3216104؛ 3307730011؛ 33286392؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7174282؛ 71742824؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3216104؛ 3307730011؛ 33286392؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7133,7 +7181,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>36,171؛ 30,000؛ 25,000؛ 22,500؛ 20,000؛ 3,325؛ 2,000؛ 1,902؛ 1,013؛ 1,000</t>
+          <t>36,171؛ 30,000؛ 3,325؛ 2,000؛ 1,000</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7191,7 +7239,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>60,900؛ 60,000؛ 30,000؛ 26,100؛ 25,096؛ 20,000</t>
+          <t>60,900؛ 60,000؛ 30,000؛ 20,000</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7427,11 +7475,7 @@
           <t>2011/12/14؛ 2012/01/14؛ 2012/02/13؛ 2012/03/13؛ 2012/04/07؛ 2012/05/08؛ 2012/06/09؛ 2012/07/11؛ 2012/08/11؛ 2012/09/11؛ 2012/10/09</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>10,851</t>
-        </is>
-      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
@@ -7472,7 +7516,7 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>006582؛ 008929؛ 019519؛ 059551916؛ 095160؛ 11100321؛ 1451241؛ 172602031؛ 20000000؛ 2001200؛ 2002006؛ 200266؛ 206950؛ 210090؛ 210200؛ 210250؛ 250115؛ 4030092091؛ 420821915251؛ 5059115؛ 519175؛ 54419118؛ 5451911؛ 5495191؛ 552081</t>
+          <t>006582؛ 008929؛ 059551916؛ 095160؛ 11100321؛ 119810؛ 1451241؛ 172602031؛ 20000000؛ 2001200؛ 2002006؛ 200266؛ 206950؛ 210090؛ 210200؛ 210250؛ 250115؛ 4030092091؛ 420821915251؛ 5059115؛ 519175؛ 54419118؛ 5451911؛ 5495191؛ 552081</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7539,11 +7583,7 @@
           <t>2/16/2014؛ 2013/11/09؛ 2014/01/12؛ 2014/02/10؛ 2014/03/12؛ 2014/04/13</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>9,290؛ 9,240</t>
-        </is>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
@@ -7765,11 +7805,7 @@
           <t>2011/12/14؛ 2012/01/14؛ 2012/02/13؛ 2012/03/13؛ 2012/04/07؛ 2012/05/08؛ 2012/06/09؛ 2012/07/11؛ 2012/08/11؛ 2012/09/11؛ 2012/10/09</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>19,000,500؛ 35,000؛ 1,318</t>
-        </is>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
@@ -8026,7 +8062,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1037108001؛ 1065216؛ 1098908278؛ 137136؛ 2015216؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 267049؛ 27651219؛ 3216104؛ 3218883</t>
+          <t>000000؛ 000000001؛ 0000005؛ 000844؛ 0505620363؛ 1000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8041,7 +8077,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
+          <t>450,000؛ 50,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8224,7 +8260,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8234,12 +8270,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8312,12 +8348,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2019/01/01؛ 2024-1-25؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8558,7 +8594,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1010216؛ 1017092733؛ 1030199102؛ 1037108001؛ 1065216؛ 1065416؛ 1098908278؛ 1216090؛ 137136؛ 2010316؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 27651219</t>
+          <t>000000؛ 000000001؛ 000844؛ 0505620363؛ 1000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1030199102؛ 1037108001؛ 1098908278؛ 1216090؛ 137136؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 27651219؛ 2824717؛ 30077461؛ 3216104؛ 3218883؛ 33125567</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8573,7 +8609,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>100,000,000؛ 500,000؛ 450,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
+          <t>500,000؛ 450,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8640,7 +8676,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1037108001؛ 1065216؛ 1098908278؛ 137136؛ 2015216؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 267049؛ 27651219؛ 3216104؛ 3218883</t>
+          <t>000000؛ 000000001؛ 0000005؛ 000844؛ 0505620363؛ 1000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8655,7 +8691,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
+          <t>450,000؛ 50,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8740,7 +8776,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>3؛ 21؛ 80؛ 85؛ 141</t>
+          <t>21؛ 80؛ 85؛ 141</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -8792,7 +8828,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8802,12 +8838,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -8863,10 +8899,14 @@
           <t>42824717</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 220022290147211943؛ 2261420354؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 244441؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 3372907101؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849</t>
+          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9086,7 +9126,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>100000000؛ 1008017301؛ 1015216؛ 1015219؛ 1095416؛ 2015216؛ 347149؛ 4030077461؛ 4030094825؛ 6065416؛ 616089</t>
+          <t>000000001؛ 100000000؛ 1008017301؛ 347149؛ 4030077461؛ 4030094825؛ 5216102؛ 5416901؛ 6065416؛ 6125101؛ 616089؛ 9125101</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9097,7 +9137,7 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>100,000,000؛ 46,000؛ 1,000</t>
+          <t>100,000,000؛ 1,000</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -9214,7 +9254,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9224,12 +9264,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9353,11 +9393,7 @@
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>176</t>
@@ -9449,11 +9485,7 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
-        </is>
-      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>176</t>
@@ -9508,7 +9540,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9518,12 +9550,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9590,7 +9622,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9600,12 +9632,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9908,22 +9940,22 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431 / 09 / 20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13؛ 1445 / 03 / 13</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10388,22 +10420,22 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431 / 09 / 20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09 / 06 / 1446؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024 - 10 - 30؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024 - 10 - 30؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10636,7 +10668,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847؛ 1037108001؛ 104200040؛ 10550220؛ 1064274077؛ 1064690371</t>
+          <t>000002؛ 00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 0992731؛ 10001111؛ 10001191؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847؛ 1037108001</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10646,12 +10678,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>1932/12/06؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
+          <t>1932/12/06؛ 2012/12/15؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>79,929,906؛ 36,877,936؛ 150,000؛ 17,000؛ 450؛ 268؛ 120</t>
+          <t>150,000؛ 17,000؛ 450؛ 268؛ 120</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10666,7 +10698,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>1؛ 8؛ 96؛ 100؛ 202</t>
+          <t>1؛ 8؛ 100؛ 202</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -10888,7 +10920,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10898,12 +10930,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -645,52 +645,56 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>د. محمد البنا؛ القاضي الزايدي</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>د. محمد البنا؛ القاضي الزايدي؛ القاضي اللحيدان</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>42824717</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102</t>
+          <t>000844؛ 077617؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015957؛ 1017092733؛ 110177؛ 141157؛ 141721؛ 1790151771151577؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25؛ 1432-11-07؛ 1432-12-02؛ 1432/12/2؛ 1433-06-08</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2023/09/20</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>12/2/1432؛ 12/3/1433؛ 12/4/1438؛ 1431-09-20؛ 1432-02-22؛ 1438-11-25؛ 1445-02-20؛ 1445-02-29؛ 1445-03-04؛ 16/11/1444؛ 18/11/1393؛ 20/09/1431؛ 26/06/1444؛ 26/7/1434؛ 29/ 02/ 1445؛ 4/3/1432؛ 8/6/1433</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,779,770؛ 3,000,000؛ 1,777,977؛ 450,000</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام الشركات؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 66؛ 76؛ 78؛ 87؛ 93؛ 157؛ 158؛ 165</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -715,52 +719,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>د. محمد البنا؛ القاضي الزايدي</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>القاضي اللحيدان</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>42824717</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25؛ 1432-11-07؛ 1432-12-02؛ 1432/12/2؛ 1433-06-08</t>
-        </is>
-      </c>
+          <t>000006؛ 000844؛ 1007056847؛ 1008017301؛ 1017092733؛ 117112؛ 117405؛ 40111151؛ 42824717؛ 4570053093؛ 878577</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2023/09/20</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>04/10/2010</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>478,757,110؛ 11,574,017؛ 450,000؛ 170؛ 135؛ 17</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>08؛ 47؛ 51؛ 69؛ 78؛ 86؛ 200؛ 201</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -3427,7 +3435,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -3444,23 +3452,31 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1000017301؛ 1007056837؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 13964648177؛ 2261420354؛ 27651219؛ 400344502394972؛ 401024501240718؛ 42824717؛ 4530241622؛ 466019273؛ 4731461703؛ 744441؛ 7486507001؛ 804332242؛ 804620836</t>
+          <t>00001117701؛ 1007056837؛ 1007056847؛ 1008017301؛ 101519؛ 101719؛ 1723101001؛ 18125511؛ 27651219؛ 304332242؛ 304620836؛ 401024501240718؛ 42824717؛ 4530241622؛ 466019273؛ 478741711؛ 7517757؛ 771011719؛ 7792491؛ 914511</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>05 / 10 / 1441؛ 08 / 01 / 1447؛ 08 / 04 / 1445؛ 1445 / 04 / 08؛ 1445-01-01؛ 1445/03/13؛ 1445/04/7؛ 1445/04/8؛ 1445/08/25؛ 1447 / 04 / 13؛ 1447/04/13؛ 25 / 08 / 1445</t>
+          <t>1440/4/1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>1,445</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>01؛ 3؛ 4؛ 15؛ 17؛ 29؛ 57؛ 69؛ 159</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -3485,28 +3501,44 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>4630548401</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1017092733؛ 1037108001؛ 144447؛ 401024501240718؛ 4630371972؛ 4713404041؛ 4713765960؛ 4731639254؛ 4731814153؛ 7486507001؛ 77186464931</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>1007056847؛ 1008017301؛ 101719؛ 111107؛ 1415187؛ 330272727؛ 401024501240718؛ 4630371972؛ 4630548401؛ 4713404041؛ 4713765960؛ 4731461703؛ 4731639254؛ 4771864931؛ 51471141؛ 7441864931؛ 804332242؛ 804620836؛ 8525911؛ 8714114111؛ 9171775</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>03 / 06 / 1447؛ 24/04/1446؛ 25/08/1445</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>محكمة الاستئناف / دائرة الاستئناف</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات؛ نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>3؛ 9؛ 17؛ 28؛ 87؛ 184؛ 190؛ 200</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -5637,20 +5669,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>214178117؛ 241474111؛ 2518141107؛ 38391575؛ 3855849؛ 4030196102؛ 43281449</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5658,7 +5694,7 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -5682,25 +5718,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>مستند مالي</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>111114؛ 2417814017؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 47814011</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5708,7 +5748,7 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -5737,20 +5777,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>2578148017؛ 33333777277؛ 38391575؛ 3855849؛ 4030196102؛ 41814117؛ 43281449</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5758,7 +5802,7 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -5787,20 +5831,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>21414117؛ 38391575؛ 3855849؛ 4030196102؛ 41418107؛ 43281449؛ 47814117</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5808,7 +5856,7 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -5837,20 +5885,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>21414117؛ 2414781107؛ 2478148117؛ 38391575؛ 3855849؛ 4030196102؛ 43281449</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5858,7 +5910,7 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -5887,20 +5939,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 5005120801؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>15918151107؛ 241478107؛ 333333337777777؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 57404011</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5908,7 +5964,7 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -5937,20 +5993,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>117114؛ 159178151117؛ 247814117؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 55404017</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5958,7 +6018,7 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -5987,20 +6047,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
+          <t>111114؛ 221414117؛ 257414117؛ 38391575؛ 3855849؛ 4030196102؛ 43281449</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -6008,7 +6072,7 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -6037,32 +6101,32 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>22/10/1444</t>
-        </is>
-      </c>
+          <t>1541781751117؛ 38391575؛ 3855849؛ 4030196102؛ 417814111؛ 41874111؛ 43281449؛ 4403035471</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -6091,32 +6155,32 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4403035471؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>22/10/1444</t>
-        </is>
-      </c>
+          <t>111114؛ 241418107؛ 38391575؛ 3855849؛ 4030196102؛ 43281449؛ 4403635471؛ 5181117؛ 57414111</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -6145,32 +6209,32 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1432-11-07؛ 20/9/1431؛ 7/11/1432</t>
-        </is>
-      </c>
+          <t>0000022222220؛ 01000070؛ 101111467؛ 1111114؛ 2141748751107؛ 21417874017؛ 2758175؛ 333333337373777؛ 38391575؛ 3855849؛ 4030196102؛ 41474110؛ 41874107؛ 43281449</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -6199,32 +6263,32 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3307730011؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1432-11-07؛ 20/9/1431؛ 7/11/1432</t>
-        </is>
-      </c>
+          <t>1591414110؛ 247814017؛ 261414110؛ 38391575؛ 3855849؛ 4030196102؛ 414154107؛ 43281449</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -6253,36 +6317,36 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>القاضي الزايدي</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)؛ القاضي الزايدي؛ القاضي اللحيدان</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0525603701؛ 1037108001؛ 1095479901؛ 144442؛ 1708291111؛ 1850147901؛ 2824717؛ 3216104؛ 3307730011؛ 33286392؛ 3372907101؛ 38391575؛ 3855849؛ 4030196102؛ 42824717؛ 43281449؛ 4506416501؛ 4688841101؛ 6084404401؛ 6914911101؛ 7486507001؛ 7704726401؛ 8350582211؛ 8728098901</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>08/06/1433؛ 10/2/1434؛ 22/02/1432</t>
-        </is>
-      </c>
+          <t>111111؛ 14178741107؛ 21417874017؛ 23092230؛ 2758175؛ 3216104؛ 33286392؛ 38391575؛ 3855849؛ 4030196102؛ 417474110؛ 418140117؛ 418141107؛ 43281449؛ 9775015</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -6443,36 +6507,52 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>القاضي الزايدي</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)؛ القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0525603701؛ 1007056847؛ 1017092733؛ 1037108001؛ 1095479901؛ 1708291111؛ 1850147901؛ 229014721194320022؛ 244441؛ 3218883؛ 3307730011؛ 331882138؛ 33286392؛ 3372907101؛ 38391575؛ 3855849؛ 4030169102؛ 4030196102؛ 4228122؛ 43281449؛ 4403035471؛ 4470094084؛ 4470635209؛ 4470652975؛ 4470913988</t>
+          <t>0111111200؛ 1007056847؛ 1017092733؛ 1417415117؛ 1434102110؛ 191797؛ 229014721194320022؛ 2474740107؛ 257405111؛ 3218883؛ 33286392؛ 333333770707277؛ 38391575؛ 3855849؛ 4030169102؛ 4030196102؛ 4178140107؛ 4228122؛ 43281449؛ 4403035471؛ 4417019554؛ 45414111؛ 4781761117؛ 5057910؛ 57415117</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1/1/1445؛ 1/12/1442؛ 1/8/1444؛ 10/11/1444؛ 11/4/1437؛ 12/05/1438؛ 16/10/1431؛ 18/11/1393؛ 2/12/1432؛ 2/4/1444؛ 20/09/1431؛ 20/9/1431؛ 22/10/1444؛ 25/07/1432؛ 4/3/1432؛ 8/6/1433؛ 9/11/1443</t>
+          <t>18/11/1393</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 27,932,012؛ 27,651,219؛ 450,000</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>25؛ 26؛ 29؛ 40؛ 41؛ 76؛ 86؛ 87</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -8885,52 +8965,56 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>د. محمد البنا؛ القاضي الزايدي</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+          <t>د. محمد البنا؛ المحامي الشهري؛ القاضي الزايدي؛ القاضي اللحيدان</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>42824717</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 37153592؛ 38391575؛ 38403785؛ 3855849؛ 4030169102</t>
+          <t>000844؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015957؛ 1017092733؛ 1107177؛ 111177؛ 11710151771151577؛ 141721؛ 157815549؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 2758752؛ 3216104؛ 3218883؛ 33125567؛ 33286392؛ 34200931؛ 34281449؛ 342881449؛ 3431443؛ 3511754؛ 37153592</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04؛ 1432-06-08؛ 1432-07-25؛ 1432-11-07؛ 1432-12-02؛ 1432/12/2؛ 1433-06-08</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>2023/09/20</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>10/ 03/ 1445؛ 12/2/1432؛ 12/3/1433؛ 12/4/1438؛ 1431-09-20؛ 1432-02-22؛ 1438-11-25؛ 1445-02-20؛ 1445-02-29؛ 1445-03-04؛ 16/11/1444؛ 18/11/1393؛ 20/09/1431؛ 26/06/1444؛ 26/7/1434؛ 4/3/1432؛ 8/6/1433</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,775,770؛ 17,717,977؛ 3,000,000؛ 450,000</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>ديوان المظالم</t>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم؛ المحكمة العليا</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام الشركات؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 76؛ 78؛ 87؛ 93؛ 157؛ 158؛ 165</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -594,33 +594,49 @@
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>4431025114</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1008017301؛ 144442؛ 2824717؛ 3372907101؛ 42824717؛ 4431025114؛ 7486507001</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>0199507؛ 1007056839؛ 1008017301؛ 1771797؛ 17787151؛ 20701157511؛ 20701197101؛ 22711584115؛ 22711784115؛ 275875؛ 3218883؛ 33286392؛ 34281449؛ 38391575؛ 3855849؛ 4030016974؛ 4030042496؛ 4030048620؛ 4030054187؛ 4030077461؛ 4030092091؛ 4030092507؛ 4030092518؛ 4030094825؛ 4030107003</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2/11/1443؛ 20/9/1431</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>71,218,857,178؛ 372,426,828؛ 368,757,931؛ 120,000,000؛ 78,000,000؛ 10,000,000؛ 9,177,747؛ 500,000؛ 450,000؛ 120</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>المحكمة التجارية بجدة</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -857,17 +873,41 @@
           <t>حكم / صك</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0017057105؛ 006060606060600؛ 0078640؛ 01018009177011؛ 0153375557؛ 0156707041؛ 0701111؛ 1070601؛ 170001576511؛ 17000186؛ 170019؛ 202064؛ 212122221212121212271727272727272717121212121؛ 417000؛ 4170155517؛ 41709711007؛ 5070171101؛ 517000011551؛ 51700511؛ 5176501</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1/17/1460</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>50,484,843,715؛ 8,849,447,678؛ 184,887,445؛ 8,844,470؛ 87,445</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>نظام الشركات</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
@@ -4471,42 +4511,42 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>4431025114؛ 4530241622</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3218883؛ 33286392؛ 3855849؛ 403016؛ 42824717؛ 4431025114؛ 4530241622</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>01 / 01 / 1445؛ 13 / 03 / 1445؛ 13 /3/ 1445؛ 1438 / 10 / 25؛ 18 /2/ 1442؛ 2/ 12 / 1431؛ 2/ 12 / 1432؛ 20 / 09 / 1431؛ 25 / 12 / 1442؛ 8/6/ 1432؛ 8/6/ 1433</t>
-        </is>
-      </c>
+          <t>0000000؛ 070117551571؛ 10100010001؛ 372777537؛ 45707515571؛ 517171؛ 5570751777؛ 571188485؛ 57510175111؛ 57751711؛ 5855859</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات؛ اللائحة التنفيذية؛ نظام الاثبات؛ نظام الإثبات</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>72</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -4765,16 +4805,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>4530241622</t>
@@ -4782,19 +4822,23 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>42824717؛ 4530241622</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>100103؛ 4530241622؛ 4570053093</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1445/ 08/16</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>20,043,862</t>
+          <t>135؛ 120</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+          <t>محكمة الاستئناف / دائرة الاستئناف</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6380,7 +6424,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>تركي بن رابح المطيري (وكيل)</t>
+          <t>تركي بن رابح المطيري (وكيل)؛ محمد الثعلي (وكيل)؛ القاضي الزايدي؛ القاضي اللحيدان</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6388,31 +6432,27 @@
           <t>شركة أحمد زيني التجارية</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1008017301؛ 1017092733؛ 3216104؛ 33286392؛ 4030196102؛ 42824717</t>
+          <t>111114؛ 247814017؛ 3216104؛ 33286392؛ 38391575؛ 3855849؛ 4030196102؛ 417414110؛ 41814017؛ 43281449؛ 51814117؛ 775015</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>08/06/1433؛ 10/2/1434؛ 22/02/1432؛ 24-11-1444</t>
+          <t>10/ 2/ 1438</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>372,426,828؛ 368,757,931؛ 335,184,145؛ 97,762,042؛ 27,932,012؛ 450,000</t>
+          <t>372,426,828؛ 120</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>المحكمة التجارية بجدة</t>
+          <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -693,7 +693,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,779,770؛ 3,000,000؛ 1,777,977؛ 450,000</t>
+          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,779,770؛ 3,000,000؛ 1,777,977؛ 450,000؛ 135</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>المحامي الشهري</t>
+          <t>د. محمد البنا</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -823,14 +823,10 @@
           <t>42824717</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4630548401</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1017092733؛ 42824717؛ 4611037394؛ 4630548401</t>
+          <t>1007056847؛ 1008017301؛ 1017092733؛ 114787121؛ 2333332323327؛ 278515؛ 42824717؛ 4611037394؛ 4630371972</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -843,7 +839,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1578,7 +1574,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1008017301؛ 1032142174؛ 1048317232؛ 1048345209؛ 1051388؛ 180000؛ 229014721194320022؛ 312019؛ 312069؛ 319069؛ 3219104؛ 32328224؛ 33125567؛ 33286392؛ 387853؛ 567889؛ 7050832001؛ 910213؛ 990212؛ 990213</t>
+          <t>1002380507؛ 1008017301؛ 1032142174؛ 1048317232؛ 1048345209؛ 1051388؛ 180000؛ 229014721194320022؛ 312019؛ 312069؛ 319069؛ 3219104؛ 32328224؛ 33125567؛ 33286392؛ 387853؛ 567889؛ 910213؛ 990212؛ 990213</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2206,7 +2202,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>000000؛ 00000000؛ 00000000014؛ 00000000016؛ 00000000020؛ 000009؛ 000038؛ 00011600013؛ 0001212؛ 00037805750؛ 0006080231497؛ 001096؛ 00970212؛ 01382699400؛ 0211318؛ 0380421؛ 0558833456؛ 10000000؛ 100000000؛ 100004242؛ 1013048699940؛ 1055022؛ 1080000؛ 110001079؛ 11323119</t>
+          <t>000000؛ 00000000؛ 00000000014؛ 00000000016؛ 00000000020؛ 000038؛ 00011600013؛ 0001212؛ 00037805750؛ 0006080231497؛ 001096؛ 00970212؛ 01382699400؛ 0211318؛ 0380421؛ 0558833456؛ 10000000؛ 100000000؛ 100004242؛ 1013048699940؛ 1055022؛ 1080000؛ 110001079؛ 11323119؛ 11323368</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2221,7 +2217,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>250,000,000؛ 217,250,000؛ 172,613,467؛ 172,613,466؛ 140,000,000؛ 100,000,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 17,635,241؛ 11,679,151؛ 10,730,000؛ 5,850,000؛ 2,500,000؛ 1,974,805؛ 1,943,903؛ 1,900,000؛ 1,527,778؛ 1,170,000؛ 1,000,000؛ 856,255؛ 833,333؛ 650,000؛ 590,000</t>
+          <t>250,000,000؛ 217,250,000؛ 172,613,467؛ 172,613,466؛ 140,000,000؛ 100,000,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 17,635,241؛ 11,679,151؛ 10,730,000؛ 5,850,000؛ 2,500,000؛ 1,974,805؛ 1,943,903؛ 1,900,000؛ 1,527,778؛ 1,170,000؛ 1,000,000؛ 900,000؛ 856,255؛ 833,333؛ 650,000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2622,7 +2618,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>010214030؛ 1008017301؛ 1017092733؛ 1055220915؛ 105522923؛ 1057980839؛ 1902900403؛ 199642؛ 2019403016؛ 3007014030؛ 4030016974؛ 4030042496؛ 4030048620؛ 4030094825؛ 4517014030؛ 7052403009؛ 7814030054؛ 8152940300؛ 849430</t>
+          <t>010214030؛ 1008017301؛ 1017092733؛ 1055220915؛ 105522923؛ 1057980839؛ 1902900403؛ 199642؛ 3007014030؛ 4030016974؛ 4030042496؛ 4030048620؛ 4030092518؛ 4030094825؛ 4030169102؛ 4517014030؛ 7052403009؛ 7814030054؛ 849430</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4246,13 +4242,17 @@
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>42824717</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>القاضي اللحيدان</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>4530241622</t>
@@ -4260,25 +4260,29 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>42824717؛ 4530241622</t>
+          <t>000844؛ 4530241622</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2010/10/04</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>79,924,901</t>
+          <t>450,000؛ 170؛ 120</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ ديوان المظالم</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>47؛ 69؛ 78؛ 185</t>
+          <t>47؛ 69؛ 78</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5336,7 +5340,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>310041499400003؛ 33286392؛ 4030196102؛ 6550303؛ 6550707؛ 6554777؛ 7070655</t>
+          <t>310041499400003؛ 33286392؛ 4030196102؛ 6550303؛ 6550707؛ 6554777</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5506,7 +5510,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>16554777؛ 310041499400003؛ 42824717؛ 6550303؛ 6550707؛ 6554777؛ 7070655</t>
+          <t>16554777؛ 310041499400003؛ 42824717؛ 6550303؛ 6550707؛ 6554777</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5564,7 +5568,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>16554777؛ 310041499400003؛ 421109157؛ 42824717؛ 6550303؛ 6550707؛ 6554777؛ 7070655؛ 725111124</t>
+          <t>16554777؛ 310041499400003؛ 421109157؛ 42824717؛ 6550303؛ 6550707؛ 6554777؛ 725111124</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -6378,7 +6382,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>111111؛ 14178741107؛ 21417874017؛ 23092230؛ 2758175؛ 3216104؛ 33286392؛ 38391575؛ 3855849؛ 4030196102؛ 417474110؛ 418140117؛ 418141107؛ 43281449؛ 9775015</t>
+          <t>14178741107؛ 21417874017؛ 23092230؛ 2758175؛ 3216104؛ 33286392؛ 38391575؛ 3855849؛ 4030196102؛ 417474110؛ 418140117؛ 418141107؛ 43281449؛ 9775015</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6622,39 +6626,51 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>المحامي الشهري</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>القاضي اللحيدان</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>شركة أحمد زيني التجارية</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>42824717</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>4530828230</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1007056847؛ 1008017301؛ 1017092733؛ 42824717؛ 4530828230</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>13/03/1445؛ 1445/08/25؛ 25-08-1445</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+          <t>000006؛ 000844؛ 1007056847؛ 1008017301؛ 1017092733؛ 117112؛ 117405؛ 40111151؛ 42824717؛ 4570053093؛ 878577</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>04/10/2010</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>478,757,110؛ 11,574,017؛ 450,000؛ 170؛ 135؛ 17</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+          <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المحاكم التجارية؛ نظام المرافعات؛ اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>08؛ 47؛ 51؛ 69؛ 78؛ 86؛ 200؛ 201</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -9037,7 +9053,7 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,775,770؛ 17,717,977؛ 3,000,000؛ 450,000</t>
+          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,775,770؛ 17,717,977؛ 3,000,000؛ 450,000؛ 135</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9052,7 +9068,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 76؛ 78؛ 87؛ 93؛ 157؛ 158؛ 165</t>
+          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 66؛ 76؛ 78؛ 87؛ 93؛ 157؛ 158؛ 165</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -2629,7 +2629,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3,681,664,891؛ 3,048,489,219؛ 1,840,832,446؛ 1,769,886,051؛ 1,524,244,610؛ 884,943,025؛ 5,000,001؛ 1,808,346</t>
+          <t>3,681,664,891؛ 3,048,489,219؛ 1,840,832,446؛ 1,769,886,051؛ 1,524,244,610؛ 884,943,025؛ 5,000,001؛ 1,808,346؛ 100,000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>33؛ 76</t>
+          <t>16؛ 33؛ 76</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -693,7 +693,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,779,770؛ 3,000,000؛ 1,777,977؛ 450,000؛ 135</t>
+          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,779,770؛ 3,000,000؛ 1,777,977؛ 450,000؛ 622؛ 135</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 66؛ 76؛ 78؛ 87؛ 93؛ 157؛ 158؛ 165</t>
+          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 66؛ 76؛ 78؛ 86؛ 87؛ 93؛ 157؛ 158؛ 165</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>478,757,110؛ 11,574,017؛ 450,000؛ 170؛ 135؛ 17</t>
+          <t>478,757,110؛ 368,757,931؛ 11,574,017؛ 450,000؛ 170؛ 135؛ 120؛ 17</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1041,7 +1041,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>368,757,931؛ 331,882,138؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 450,000؛ 120</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1266,7 +1266,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0022971؛ 0504302223؛ 1985888؛ 2821277؛ 4030169102؛ 42824717؛ 7171971؛ 8687266</t>
+          <t>0504302223؛ 1791717؛ 1792200؛ 1985888؛ 2821277؛ 4030169102؛ 42824717؛ 8687255؛ 8687266</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0022971؛ 42824717؛ 5527868؛ 7171971؛ 7721282؛ 8687266؛ 888891</t>
+          <t>1791717؛ 1792200؛ 198888؛ 2821277؛ 42824717؛ 8687255؛ 8687266</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1002380507؛ 1008017301؛ 1032142174؛ 1048317232؛ 1048345209؛ 1051388؛ 180000؛ 229014721194320022؛ 312019؛ 312069؛ 319069؛ 3219104؛ 32328224؛ 33125567؛ 33286392؛ 387853؛ 567889؛ 910213؛ 990212؛ 990213</t>
+          <t>1002380507؛ 1008017301؛ 1032142174؛ 1048317232؛ 1048345209؛ 1051388؛ 180000؛ 212099؛ 229014721194320022؛ 312019؛ 312069؛ 312099؛ 319069؛ 3219104؛ 32328224؛ 33125567؛ 33286392؛ 387853؛ 567889</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1؛ 5؛ 6؛ 78؛ 79؛ 239</t>
+          <t>1؛ 5؛ 6؛ 78؛ 79؛ 129؛ 239</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1807,7 +1807,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>02 / 12 / 1432؛ 10 / 02 / 1434؛ 16 / 10 / 1431</t>
+          <t>02 / 12 / 1432؛ 1431 / 10 / 16؛ 1434 / 02 / 10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2202,22 +2202,22 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>000000؛ 00000000؛ 00000000014؛ 00000000016؛ 00000000020؛ 000038؛ 00011600013؛ 0001212؛ 00037805750؛ 0006080231497؛ 001096؛ 00970212؛ 01382699400؛ 0211318؛ 0380421؛ 0558833456؛ 10000000؛ 100000000؛ 100004242؛ 1013048699940؛ 1055022؛ 1080000؛ 110001079؛ 11323119؛ 11323368</t>
+          <t>000000؛ 00000000؛ 00000000014؛ 00000000016؛ 00000000020؛ 000038؛ 00011600013؛ 00037805750؛ 0006080231497؛ 001096؛ 01382699400؛ 0211318؛ 0380421؛ 0558833456؛ 10000000؛ 100000000؛ 100004242؛ 1013048699940؛ 1055022؛ 1080000؛ 110001079؛ 11323119؛ 11323368؛ 11324890؛ 1161000905</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01-01-1430؛ 09/08/1431؛ 10/19/1431؛ 1411/8/30؛ 1413/10/26؛ 1424/9/6؛ 1426/07/18؛ 1430/10/1؛ 1432/06/07؛ 1432/4/10؛ 1432/4/30؛ 23/01/1432؛ 29-12-1430؛ 8/15/1431؛ 9/22/1431</t>
+          <t>01-01-1430؛ 09/08/1431؛ 10/19/1431؛ 1411/8/30؛ 1413/10/26؛ 1423/12/30؛ 1424/9/6؛ 1426/07/18؛ 1430/10/1؛ 1432/06/07؛ 1432/4/10؛ 1432/4/30؛ 23/01/1432؛ 29-12-1430؛ 8/15/1431؛ 9/22/1431</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>07-05-2011؛ 10/5/2011؛ 11-04-2010؛ 11-07-2010؛ 11/12/2010؛ 16-03-2010؛ 16-05-2010؛ 16-06-2010؛ 18-06-2011؛ 18-10-2010؛ 19-08-2010؛ 19-12-2010؛ 20/12/2010؛ 2003/11/1؛ 2009/04/01؛ 2009/12/21؛ 2010/5/1؛ 2011/5/1؛ 21-02-2011؛ 21-07-2010؛ 21/07/2010؛ 22-11-2010؛ 24-04-2011؛ 26-06-2011؛ 26-09-2010</t>
+          <t>07-05-2011؛ 10/ 5 / 2017؛ 10/5/2011؛ 11-04-2010؛ 11-07-2010؛ 11/12/2010؛ 16-03-2010؛ 16-05-2010؛ 16-06-2010؛ 18-06-2011؛ 18-10-2010؛ 19-08-2010؛ 19-12-2010؛ 20/12/2010؛ 2003/11/1؛ 2009/04/01؛ 2009/12/21؛ 2009/12/22؛ 2010/5/1؛ 2011/5/1؛ 21-02-2011؛ 21-07-2010؛ 21/07/2010؛ 22-11-2010؛ 24-04-2011</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>250,000,000؛ 217,250,000؛ 172,613,467؛ 172,613,466؛ 140,000,000؛ 100,000,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 17,635,241؛ 11,679,151؛ 10,730,000؛ 5,850,000؛ 2,500,000؛ 1,974,805؛ 1,943,903؛ 1,900,000؛ 1,527,778؛ 1,170,000؛ 1,000,000؛ 900,000؛ 856,255؛ 833,333؛ 650,000</t>
+          <t>250,000,000؛ 217,250,000؛ 172,613,467؛ 172,613,466؛ 140,000,000؛ 100,000,000؛ 39,495,773؛ 33,573,786؛ 28,977,000؛ 21,659,786؛ 20,000,000؛ 17,635,241؛ 11,679,151؛ 10,730,000؛ 5,850,000؛ 2,500,000؛ 1,974,805؛ 1,943,903؛ 1,900,000؛ 1,527,778؛ 1,170,000؛ 1,000,000؛ 900,000؛ 856,255؛ 833,333</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2260,14 +2260,14 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>09666685458؛ 952730؛ 96626685415</t>
+          <t>037259؛ 09666685458؛ 96626685415</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>11,679,151؛ 737,500</t>
+          <t>1,037,259,019؛ 172,613,467؛ 14,282,008؛ 11,679,151؛ 3,062,129؛ 1,943,903؛ 856,255؛ 737,500؛ 390,000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2319,7 +2319,11 @@
           <t>02/07/2013؛ 02/09/2013؛ 03/01/2013؛ 03/02/2013؛ 03/04/2013؛ 03/05/2016؛ 03/11/2010؛ 03/12/2012؛ 08/06/2017؛ 11/03/2013؛ 11/04/2013؛ 11/07/2013؛ 12/01/2013؛ 12/01/2014؛ 12/01/2015؛ 12/02/2013؛ 12/10/2014؛ 13/04/2014؛ 13/07/2014؛ 13/10/2013؛ 14/11/2013؛ 16/04/2014؛ 18/05/2013؛ 21/07/2014؛ 26/01/2017</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>3,000,000</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -2618,7 +2622,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>010214030؛ 1008017301؛ 1017092733؛ 1055220915؛ 105522923؛ 1057980839؛ 1902900403؛ 199642؛ 3007014030؛ 4030016974؛ 4030042496؛ 4030048620؛ 4030092518؛ 4030094825؛ 4030169102؛ 4517014030؛ 7052403009؛ 7814030054؛ 849430</t>
+          <t>1008017301؛ 1017092733؛ 1055220915؛ 105522923؛ 1057980839؛ 199642؛ 4030016974؛ 4030042496؛ 4030048620؛ 4030054187؛ 4030092091؛ 4030092507؛ 4030092518؛ 4030094825؛ 4030107003؛ 4030107145؛ 403012010؛ 4030169102؛ 849430</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3304,12 +3308,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2019/01/01؛ 2024-1-25؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3364,7 +3368,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>310041499400003؛ 42824717؛ 4714487917؛ 6550303؛ 6550707؛ 6554777؛ 7197471448</t>
+          <t>310041499400003؛ 42824717؛ 4714487917؛ 6550303؛ 6550707؛ 6554777</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3572,7 +3576,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>3؛ 9؛ 17؛ 28؛ 87؛ 184؛ 190؛ 200</t>
+          <t>3؛ 9؛ 17؛ 28؛ 29؛ 87؛ 184؛ 190؛ 200</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -3664,7 +3668,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>17؛ 25؛ 26؛ 200</t>
+          <t>1؛ 17؛ 25؛ 26؛ 200</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -3759,7 +3763,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>07 / 10 / 1447؛ 1447 / 04 / 13؛ 1447 / 04 / 29؛ 1447 / 09 / 09</t>
+          <t>1447 / 04 / 13؛ 1447 / 04 / 29؛ 1447 / 09 / 09؛ 1447 / 10 / 07</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -4104,7 +4108,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4271,7 +4279,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>450,000؛ 170؛ 120</t>
+          <t>368,757,931؛ 450,000؛ 170؛ 120</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4342,7 +4350,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4606,7 +4618,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4664,7 +4680,11 @@
           <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>[مخرج آلي / Script Output - سماوي]</t>
@@ -4707,7 +4727,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>04 / 03 / 1445؛ 06 / 03 / 1445</t>
+          <t>06 / 03 / 1445؛ 1445 / 03 / 04</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4893,7 +4913,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>02 / 06 / 1446؛ 13 / 03 / 1445؛ 18 / 06 / 1446؛ 28 / 04 / 1447؛ 28 / 08 / 1447</t>
+          <t>1445 / 03 / 13؛ 1446 / 06 / 02؛ 1446 / 06 / 18؛ 1447 / 04 / 28؛ 28 / 08 / 1447</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5005,7 +5025,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1432 - 11 - 07</t>
+          <t>07 - 11 - 1432</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
@@ -5062,12 +5082,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>000000؛ 000000001؛ 0000005؛ 000844؛ 0102012؛ 0126054571؛ 030420843؛ 030420883؛ 0536533388؛ 08017301؛ 100000000؛ 1007056839؛ 1007056847؛ 100791؛ 100801؛ 100801730؛ 1008017301؛ 1015318؛ 1017092733؛ 1030091825؛ 1030119102؛ 1030169102؛ 103816076؛ 1046990071؛ 1055220915</t>
+          <t>000000؛ 000844؛ 0102012؛ 0126054571؛ 030420843؛ 030420883؛ 0536533388؛ 08017301؛ 100000000؛ 1007056839؛ 1007056847؛ 100801؛ 100801730؛ 1008017301؛ 1010119؛ 1015318؛ 1017092733؛ 1018219؛ 1030091825؛ 1030119102؛ 1030169102؛ 103816076؛ 1046990071؛ 1055220915؛ 1064274077</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1/6/1442؛ 10 / 5 / 1436؛ 11/ 2 / 1434؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1413/9/8؛ 1428/3/14؛ 1428/4/18؛ 1429/12/3؛ 1430/4/4؛ 1432/11/21؛ 1432/2/13؛ 1432/6/26؛ 1438/07/26؛ 1438/3/14؛ 1438/4/18؛ 1442/06/28؛ 1442/5/9؛ 1445/03/13؛ 1445/03/20؛ 1446/03/20؛ 2/ 2 / 1434؛ 2/15/ 1392؛ 8/ 2 / 1432</t>
+          <t>1/6/1442؛ 10 / 5 / 1436؛ 10/ 2 / 1434؛ 11/ 2 / 1434؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1413/9/8؛ 1428/3/14؛ 1428/4/18؛ 1429/12/3؛ 1430/4/4؛ 1432/11/21؛ 1432/2/13؛ 1432/6/26؛ 1438/07/26؛ 1438/3/14؛ 1438/4/18؛ 1439/12/3؛ 1442/06/28؛ 1442/5/9؛ 1445/03/13؛ 1445/03/20؛ 1446/03/20؛ 2/ 2 / 1434</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5077,7 +5097,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>100,000,000؛ 500,000؛ 450,000؛ 1,000؛ 120</t>
+          <t>100,000,000؛ 5,000,000؛ 500,000؛ 450,000؛ 92,000؛ 46,000؛ 1,000؛ 120</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5394,7 +5414,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1008017301؛ 16554777؛ 2019910301؛ 310041499400003؛ 4030094825؛ 4030169102؛ 4030196102؛ 450000؛ 500000؛ 6065348؛ 6065431؛ 6550303؛ 6550707؛ 6554777</t>
+          <t>1008017301؛ 1030199102؛ 16554777؛ 310041499400003؛ 4030094825؛ 4030169102؛ 4030196102؛ 450000؛ 500000؛ 6065348؛ 6065431؛ 6550303؛ 6550707؛ 6554777</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5409,7 +5429,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>450,000؛ 1,000</t>
+          <t>500,000؛ 450,000؛ 1,000</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5568,7 +5588,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>16554777؛ 310041499400003؛ 421109157؛ 42824717؛ 6550303؛ 6550707؛ 6554777؛ 725111124</t>
+          <t>16554777؛ 310041499400003؛ 421109157؛ 421117251؛ 42824717؛ 6550303؛ 6550707؛ 6554777</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -6274,12 +6294,16 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0000022222220؛ 01000070؛ 101111467؛ 1111114؛ 2141748751107؛ 21417874017؛ 2758175؛ 333333337373777؛ 38391575؛ 3855849؛ 4030196102؛ 41474110؛ 41874107؛ 43281449</t>
+          <t>0000022222220؛ 101111467؛ 1111114؛ 2141748751107؛ 21417874017؛ 2758175؛ 333333337373777؛ 38391575؛ 3855849؛ 4030196102؛ 41474110؛ 41874107؛ 43281449</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>1,000,070</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>المحكمة التجارية بجدة؛ الدائرة الأولى التجارية؛ المحكمة العامة بجدة؛ ديوان المظالم</t>
@@ -6653,7 +6677,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>478,757,110؛ 11,574,017؛ 450,000؛ 170؛ 135؛ 17</t>
+          <t>478,757,110؛ 368,757,931؛ 11,574,017؛ 450,000؛ 170؛ 135؛ 120؛ 17</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7317,7 +7341,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>36,171؛ 30,000؛ 3,325؛ 2,000؛ 1,000</t>
+          <t>36,171؛ 30,000؛ 25,000؛ 22,500؛ 20,000؛ 3,325؛ 2,000؛ 1,902؛ 1,013؛ 1,000</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7375,7 +7399,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>60,900؛ 60,000؛ 30,000؛ 20,000</t>
+          <t>60,900؛ 60,000؛ 30,000؛ 26,100؛ 25,096؛ 20,000</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7611,7 +7635,11 @@
           <t>2011/12/14؛ 2012/01/14؛ 2012/02/13؛ 2012/03/13؛ 2012/04/07؛ 2012/05/08؛ 2012/06/09؛ 2012/07/11؛ 2012/08/11؛ 2012/09/11؛ 2012/10/09</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>10,851</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
@@ -7652,7 +7680,7 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>006582؛ 008929؛ 059551916؛ 095160؛ 11100321؛ 119810؛ 1451241؛ 172602031؛ 20000000؛ 2001200؛ 2002006؛ 200266؛ 206950؛ 210090؛ 210200؛ 210250؛ 250115؛ 4030092091؛ 420821915251؛ 5059115؛ 519175؛ 54419118؛ 5451911؛ 5495191؛ 552081</t>
+          <t>006582؛ 008929؛ 019519؛ 059551916؛ 095160؛ 11100321؛ 1451241؛ 172602031؛ 20000000؛ 2001200؛ 2002006؛ 200266؛ 206950؛ 210090؛ 210200؛ 210250؛ 250115؛ 4030092091؛ 420821915251؛ 5059115؛ 519175؛ 54419118؛ 5451911؛ 5495191؛ 552081</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7719,7 +7747,11 @@
           <t>2/16/2014؛ 2013/11/09؛ 2014/01/12؛ 2014/02/10؛ 2014/03/12؛ 2014/04/13</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>9,290؛ 9,240</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
@@ -7941,7 +7973,11 @@
           <t>2011/12/14؛ 2012/01/14؛ 2012/02/13؛ 2012/03/13؛ 2012/04/07؛ 2012/05/08؛ 2012/06/09؛ 2012/07/11؛ 2012/08/11؛ 2012/09/11؛ 2012/10/09</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>19,000,500؛ 35,000؛ 1,318</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
@@ -8198,12 +8234,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>000000؛ 000000001؛ 0000005؛ 000844؛ 0505620363؛ 1000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
+          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1065216؛ 1098908278؛ 137136؛ 144442؛ 2015216؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04</t>
+          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1385 / 3 / 22</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8213,7 +8249,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>450,000؛ 50,000؛ 1,000؛ 500؛ 120</t>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -8228,7 +8264,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141</t>
+          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141؛ 250</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -8396,7 +8432,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8406,12 +8442,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8484,12 +8520,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2024-1-25؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2/26/ 2014؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/20؛ 2014/02/26؛ 2014/05/28؛ 2016/05/03؛ 2016/06/26؛ 2017/01/16؛ 2017/01/26؛ 2017/06/08؛ 2019/01/01؛ 2024-1-25؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8730,12 +8766,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>000000؛ 000000001؛ 000844؛ 0505620363؛ 1000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1030199102؛ 1037108001؛ 1098908278؛ 1216090؛ 137136؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 27651219؛ 2824717؛ 30077461؛ 3216104؛ 3218883؛ 33125567</t>
+          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1010216؛ 1017092733؛ 1030199102؛ 1065216؛ 1065416؛ 1098908278؛ 1216090؛ 137136؛ 144442؛ 2010316؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 27651219؛ 2824717؛ 30077461؛ 3216104</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/ 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/3/ 1439؛ 12/5/1438؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1428/3/14؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20</t>
+          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1/ 12/ 1442؛ 1/ 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/3/ 1439؛ 12/5/1438؛ 1385 / 3 / 17</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8745,7 +8781,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>500,000؛ 450,000؛ 1,000؛ 500؛ 120</t>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8760,7 +8796,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141</t>
+          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141؛ 250</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -8812,12 +8848,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>000000؛ 000000001؛ 0000005؛ 000844؛ 0505620363؛ 1000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092733؛ 1037108001؛ 1098908278؛ 137136؛ 144442؛ 220022290147211943؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
+          <t>000000؛ 000844؛ 0505620363؛ 1000000؛ 100000000؛ 1007056839؛ 1007056847؛ 1008017301؛ 1015219؛ 1017092733؛ 1065216؛ 1098908278؛ 137136؛ 144442؛ 2015216؛ 229014721194320022؛ 2307033671543؛ 2307033671544؛ 267049؛ 27651219؛ 2824717؛ 3216104؛ 3218883؛ 33125567؛ 33286392</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1392/2/15؛ 1411/08/03؛ 1413/10/26؛ 1431-09-20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1432-02-22؛ 1432-03-04</t>
+          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1 / 2 / 1434؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2 / 1434؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1385 / 3 / 22</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8827,7 +8863,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>450,000؛ 50,000؛ 1,000؛ 500؛ 120</t>
+          <t>100,000,000؛ 500,000؛ 450,000؛ 50,000؛ 46,000؛ 1,000؛ 500؛ 120</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8842,7 +8878,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141</t>
+          <t>1؛ 3؛ 6؛ 21؛ 80؛ 141؛ 250</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -8912,7 +8948,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>21؛ 80؛ 85؛ 141</t>
+          <t>3؛ 21؛ 80؛ 85؛ 141</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -8964,22 +9000,22 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -8994,7 +9030,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -9053,7 +9089,7 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,775,770؛ 17,717,977؛ 3,000,000؛ 450,000؛ 135</t>
+          <t>368,757,931؛ 367,757,931؛ 331,882,138؛ 120,000,000؛ 110,672,379؛ 97,762,042؛ 96,779,270؛ 79,924,901؛ 79,000,000؛ 68,424,362؛ 27,932,012؛ 27,651,219؛ 17,775,770؛ 17,717,977؛ 3,000,000؛ 450,000؛ 622؛ 135</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9068,7 +9104,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 66؛ 76؛ 78؛ 87؛ 93؛ 157؛ 158؛ 165</t>
+          <t>1؛ 2؛ 8؛ 16؛ 19؛ 20؛ 21؛ 25؛ 26؛ 29؛ 40؛ 41؛ 66؛ 76؛ 78؛ 86؛ 87؛ 93؛ 157؛ 158؛ 165</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -9266,7 +9302,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>000000001؛ 100000000؛ 1008017301؛ 347149؛ 4030077461؛ 4030094825؛ 5216102؛ 5416901؛ 6065416؛ 6125101؛ 616089؛ 9125101</t>
+          <t>100000000؛ 1008017301؛ 1015216؛ 1015219؛ 1095416؛ 2015216؛ 347149؛ 4030077461؛ 4030094825؛ 6065416؛ 616089</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9277,7 +9313,7 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>100,000,000؛ 1,000</t>
+          <t>100,000,000؛ 46,000؛ 1,000</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -9394,22 +9430,22 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9424,7 +9460,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -9533,7 +9569,11 @@
           <t>المحكمة التجارية بجدة؛ محكمة الاستئناف / دائرة الاستئناف</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
       <c r="N166" t="inlineStr">
         <is>
           <t>176</t>
@@ -9625,7 +9665,11 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية؛ نظام المرافعات</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr">
         <is>
           <t>176</t>
@@ -9680,22 +9724,22 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -9710,7 +9754,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -9762,22 +9806,22 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01؛ 1445-02-12</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9792,7 +9836,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -10080,22 +10124,22 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13؛ 1445 / 03 / 13</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431 / 09 / 20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10110,7 +10154,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -10560,22 +10604,22 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09 / 06 / 1446؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445 - 11 - 13</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431 / 09 / 20؛ 1431-10-16؛ 1431-11-03؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024 - 10 - 30؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024 - 10 - 30؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10590,7 +10634,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -10808,22 +10852,22 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>000002؛ 00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 0992731؛ 10001111؛ 10001191؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847؛ 1037108001</t>
+          <t>00004245695؛ 00034122830005؛ 000545؛ 00242000؛ 0024700014208؛ 0115328؛ 02126706766؛ 028200011805750؛ 035847؛ 0556355663؛ 0599139؛ 1007056839؛ 1007056847؛ 1008017301؛ 1017092233؛ 1017092723؛ 1017092733؛ 1021501240318؛ 1029965924؛ 1035847؛ 104200040؛ 10550220؛ 1064274077؛ 1064690371؛ 1091304</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431/4/20؛ 1434/11/24؛ 1436/09/20؛ 1436/09/25؛ 1437/09/20؛ 1445-01-01؛ 1445-02-12؛ 1445-02-20؛ 1445-3-13؛ 1445-4-7؛ 1445/03/16</t>
+          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 1423/02/20؛ 1431/4/20؛ 1434/11/24؛ 1436/09/20؛ 1436/09/25؛ 1437/09/20؛ 1445-01-01؛ 1445-02-12؛ 1445-02-20؛ 1445-3-13؛ 1445-4-7</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>1932/12/06؛ 2012/12/15؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
+          <t>1932/12/06؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/06/26؛ 2013/09/30؛ 2018/07/15؛ 2020/1/25</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>150,000؛ 17,000؛ 450؛ 268؛ 120</t>
+          <t>79,929,906؛ 36,877,936؛ 150,000؛ 17,000؛ 450؛ 268؛ 120</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10838,7 +10882,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>1؛ 8؛ 100؛ 202</t>
+          <t>1؛ 8؛ 96؛ 100؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -11060,22 +11104,22 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001111؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653</t>
+          <t>000000؛ 00000000000000؛ 00004245695؛ 00037805750؛ 000545؛ 001310؛ 0018131240005؛ 0018131590049؛ 00242000؛ 00242000142؛ 01136988؛ 01139326؛ 01139336؛ 01139958؛ 01145171؛ 01153128؛ 012605؛ 01812030010؛ 035847؛ 0392506؛ 053051؛ 0534553588؛ 053651؛ 053653؛ 0536592196</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 08/04/1445؛ 09/11/1443؛ 1/1/1445؛ 1/12/1442؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/05/1438؛ 12/5/1438؛ 1423/02/20؛ 1431-10-16؛ 1431-11-03؛ 1431-12-02؛ 1431/09/20؛ 1431/09/25؛ 1431/11/29؛ 1431/9/20؛ 1434-07-26؛ 1434/11/24؛ 1438-4-21؛ 1445-01-01</t>
+          <t>01/ 09/ 1442؛ 01/08/1444؛ 02/04/1444؛ 02/12/1432؛ 06/ 11/ 1442؛ 08/04/1445؛ 09/11/1443؛ 1/ 12/ 1442؛ 1/1/1445؛ 1/12/1442؛ 10/ 2/ 1434؛ 10/ 2/ 1438؛ 10/11/1444؛ 10/2/1434؛ 11/11/1444؛ 11/4/1437؛ 12/ 2/ 1432؛ 12/ 3/ 1433؛ 12/ 4/ 1438؛ 12/05/1438؛ 12/5/1438؛ 1385 / 3 / 17؛ 14/ 10/ 1427؛ 14/ 3/ 1428؛ 1423/02/20</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>03-11-2010؛ 2010/11/03؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
+          <t>03-11-2010؛ 2010/11/03؛ 2011/12/15؛ 2012/12/1؛ 2012/12/15؛ 2013/05/02؛ 2013/06/26؛ 2013/09/30؛ 2014/01/01؛ 2014/01/20؛ 2014/02/26؛ 2014/2/26؛ 2016/05/03؛ 2016/06/26؛ 2017/01/26؛ 2017/06/08؛ 2018/05/28؛ 2024-1-25؛ 2024/01/16؛ 2024/1/21؛ 2024/1/23</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>368,757,931؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
+          <t>368,757,931؛ 331,882,138؛ 137,631,929؛ 79,924,901؛ 6,061,304؛ 2,020,000؛ 150,000؛ 17,000؛ 1,000؛ 450؛ 368؛ 120</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11090,7 +11134,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202</t>
+          <t>1؛ 58؛ 86؛ 200؛ 201؛ 202؛ 250</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -1807,7 +1807,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>02 / 12 / 1432؛ 1431 / 10 / 16؛ 1434 / 02 / 10</t>
+          <t>1431 / 10 / 16؛ 1432 / 12 / 02؛ 1434 / 02 / 10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2319,11 +2319,7 @@
           <t>02/07/2013؛ 02/09/2013؛ 03/01/2013؛ 03/02/2013؛ 03/04/2013؛ 03/05/2016؛ 03/11/2010؛ 03/12/2012؛ 08/06/2017؛ 11/03/2013؛ 11/04/2013؛ 11/07/2013؛ 12/01/2013؛ 12/01/2014؛ 12/01/2015؛ 12/02/2013؛ 12/10/2014؛ 13/04/2014؛ 13/07/2014؛ 13/10/2013؛ 14/11/2013؛ 16/04/2014؛ 18/05/2013؛ 21/07/2014؛ 26/01/2017</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>3,000,000</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -7622,7 +7618,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>0000000؛ 0000277؛ 000028؛ 077782؛ 095535؛ 107812؛ 109355؛ 110003317؛ 110035317؛ 11112200110187463؛ 111432؛ 113257؛ 115777؛ 15050197؛ 17095141916؛ 17554195؛ 17594197؛ 4030092091؛ 5100007102؛ 519175؛ 539553؛ 552588؛ 555115؛ 5597115؛ 5801715</t>
+          <t>0000000؛ 0000277؛ 000028؛ 077782؛ 095535؛ 107812؛ 109355؛ 110003317؛ 110035317؛ 11112200110187463؛ 111432؛ 113257؛ 115777؛ 15050197؛ 17095141916؛ 17554195؛ 17594197؛ 4030092091؛ 519175؛ 539553؛ 552588؛ 555115؛ 5597115؛ 5801715؛ 591191</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7975,7 +7971,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>19,000,500؛ 35,000؛ 1,318</t>
+          <t>19,000,500</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>

--- a/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
+++ b/zaini_case_audit_output/outputs/excel/03_extracted_legal_entities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P193"/>
+  <dimension ref="A1:P196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11248,6 +11248,164 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>القاضي الزايدي؛ القاضي اللحيدان</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>03893304؛ 0969455201؛ 1037108001؛ 19555323؛ 21309683؛ 21695783؛ 220023491127410922؛ 22002491127410922؛ 233071124؛ 24654204؛ 2751123؛ 29368233؛ 379810104؛ 385664404؛ 4241210304؛ 432123204؛ 5190225501؛ 5349830001؛ 57519383؛ 60004304؛ 60095904؛ 649733393؛ 67554204؛ 704701193؛ 7362470301</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>31/21/1341</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>وكالة</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>د. محمد البنا؛ القاضي الزايدي</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>1008017301؛ 1017092733؛ 1037108001؛ 103816076؛ 1046990071؛ 1055220915؛ 229014721194320022؛ 3372907101؛ 34281449؛ 391107407؛ 40340006؛ 421170332؛ 507001؛ 5130629؛ 5190225501</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1/1/1432؛ 1/6/1442؛ 12/12/1431؛ 1431 / 13/12؛ 1432 / 1 / 1؛ 1432 / 2 / 12؛ 1432 / 2 / 8؛ 1432 / 8/6؛ 1434 / 7 / 26؛ 1438 / 5 / 10؛ 1439 / 7 / 19؛ 1440 / 2 / 27؛ 1441 / 7 / 10؛ 1442 / 4 / 14؛ 1442/10/18؛ 18/2/1423؛ 18/2/1432؛ 26/7/1434</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>00000055؛ 00117157875؛ 011705371777؛ 01550771577؛ 015571710511؛ 068015؛ 105008468586؛ 1110000؛ 1448156؛ 1470088؛ 231037؛ 231432؛ 25400084؛ 300810؛ 5470688؛ 72311137؛ 74070088؛ 7410156506؛ 91848155</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1417/01/77؛ 1477/1/17؛ 1477/11/7</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
